--- a/data/archive/2026-08-10-main-ledger-archived-shadow-primary/mlb.xlsx
+++ b/data/archive/2026-08-10-main-ledger-archived-shadow-primary/mlb.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS67" headerRowCount="1">
-  <autoFilter ref="A1:CS67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS74" headerRowCount="1">
+  <autoFilter ref="A1:CS74"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$67)</f>
+        <f>COUNTA('Picks'!$A$2:$A$74)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$67,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$74,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$74,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")+COUNTIFS('Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$67,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$74,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")/(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")/(COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")+COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$67)/SUM('Picks'!$BX$2:$BX$67),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$74)/SUM('Picks'!$BX$2:$BX$74),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$67)</f>
+        <f>SUM('Picks'!$BY$2:$BY$74)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$67,"&lt;&gt;",'Picks'!$AB$2:$AB$67),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$74,"&lt;&gt;",'Picks'!$AB$2:$AB$74),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$74,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$74,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$67,'Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$74,'Picks'!$AM$2:$AM$74,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS67"/>
+  <dimension ref="A1:CS74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13758,22 +13758,22 @@
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>97896ce4943849be</t>
+          <t>bcb6241cb2b04b99</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-05T01:40Z</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>401816385</t>
+          <t>401816397</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
@@ -13810,51 +13810,73 @@
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>-163</v>
+        <v>-186</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.537634</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.65035</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.56005</v>
+        <v>0.657369</v>
       </c>
       <c r="P42" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>-0.059722</v>
+        <v>0.007019</v>
       </c>
       <c r="R42" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W42" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="X42" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v2</t>
-        </is>
-      </c>
-      <c r="U42" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V42" s="24" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="25" t="n"/>
-      <c r="Z42" s="26" t="n"/>
-      <c r="AA42" s="28" t="n"/>
-      <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n"/>
-      <c r="AD42" s="24" t="n"/>
+      <c r="Y42" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z42" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AA42" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB42" s="28" t="n">
+        <v>-0.00035</v>
+      </c>
+      <c r="AC42" s="30" t="n">
+        <v>0.9409</v>
+      </c>
+      <c r="AD42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:21:26.372391Z</t>
+        </is>
+      </c>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.87-4.68; raw selected-side p=0.5915, calibrated p=0.5601.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.19-3.76; raw selected-side p=0.7309, calibrated p=0.6574.</t>
         </is>
       </c>
       <c r="AF42" s="31" t="inlineStr">
@@ -13895,32 +13917,32 @@
       </c>
       <c r="AP42" s="24" t="inlineStr">
         <is>
-          <t>mlb-ath</t>
+          <t>mlb-det</t>
         </is>
       </c>
       <c r="AQ42" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AR42" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AS42" s="24" t="inlineStr">
         <is>
-          <t>mlb-cin</t>
+          <t>mlb-sea</t>
         </is>
       </c>
       <c r="AT42" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AU42" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AV42" s="24" t="n"/>
@@ -13938,7 +13960,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -13948,12 +13970,12 @@
       </c>
       <c r="BC42" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -13973,7 +13995,7 @@
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -13985,21 +14007,25 @@
         <v>1.5</v>
       </c>
       <c r="BK42" s="26" t="n">
-        <v>-163</v>
+        <v>-186</v>
       </c>
       <c r="BL42" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.537634</v>
       </c>
       <c r="BM42" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.65035</v>
       </c>
       <c r="BN42" s="28" t="n">
-        <v>0.616915</v>
+        <v>0.646766</v>
       </c>
       <c r="BO42" s="28" t="n"/>
       <c r="BP42" s="25" t="n"/>
-      <c r="BQ42" s="27" t="n"/>
-      <c r="BR42" s="28" t="n"/>
+      <c r="BQ42" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BR42" s="28" t="n">
+        <v>0.65</v>
+      </c>
       <c r="BS42" s="28" t="n"/>
       <c r="BT42" s="28" t="n"/>
       <c r="BU42" s="25" t="n"/>
@@ -14028,29 +14054,29 @@
       <c r="CR42" s="24" t="n"/>
       <c r="CS42" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>ddeb2a337c46426e</t>
+          <t>ce99df3a66214167</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-05T01:40Z</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>401816385</t>
+          <t>401816397</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
@@ -14060,12 +14086,12 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="H43" s="24" t="inlineStr">
@@ -14079,7 +14105,7 @@
         </is>
       </c>
       <c r="J43" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="K43" s="24" t="inlineStr">
         <is>
@@ -14087,51 +14113,73 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.480769</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.514254</v>
+        <v>0.506992</v>
       </c>
       <c r="P43" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q43" s="28" t="n">
-        <v>0.063804</v>
+        <v>0.026223</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S43" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U43" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V43" s="24" t="n"/>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
-      <c r="Y43" s="25" t="n"/>
-      <c r="Z43" s="26" t="n"/>
-      <c r="AA43" s="28" t="n"/>
-      <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n"/>
-      <c r="AD43" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W43" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="X43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z43" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="AA43" s="28" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AB43" s="28" t="n">
+        <v>-0.000769</v>
+      </c>
+      <c r="AC43" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:21:26.662275Z</t>
+        </is>
+      </c>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.87-4.68; raw selected-side p=0.5184, calibrated p=0.5143.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.19-3.76; raw selected-side p=0.5048, calibrated p=0.5070.</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -14141,7 +14189,7 @@
       </c>
       <c r="AG43" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH43" s="24" t="n"/>
@@ -14172,32 +14220,32 @@
       </c>
       <c r="AP43" s="24" t="inlineStr">
         <is>
-          <t>mlb-ath</t>
+          <t>mlb-det</t>
         </is>
       </c>
       <c r="AQ43" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AR43" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AS43" s="24" t="inlineStr">
         <is>
-          <t>mlb-cin</t>
+          <t>mlb-sea</t>
         </is>
       </c>
       <c r="AT43" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AU43" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AV43" s="24" t="n"/>
@@ -14215,7 +14263,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -14225,12 +14273,12 @@
       </c>
       <c r="BC43" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -14250,7 +14298,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -14259,24 +14307,28 @@
         </is>
       </c>
       <c r="BJ43" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK43" s="26" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.480769</v>
       </c>
       <c r="BN43" s="28" t="n">
-        <v>0.447761</v>
+        <v>0.477612</v>
       </c>
       <c r="BO43" s="28" t="n"/>
       <c r="BP43" s="25" t="n"/>
-      <c r="BQ43" s="27" t="n"/>
-      <c r="BR43" s="28" t="n"/>
+      <c r="BQ43" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR43" s="28" t="n">
+        <v>0.48</v>
+      </c>
       <c r="BS43" s="28" t="n"/>
       <c r="BT43" s="28" t="n"/>
       <c r="BU43" s="25" t="n"/>
@@ -14312,22 +14364,22 @@
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>6811d5d9494c4c1f</t>
+          <t>67f54f960d2240f2</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-05T01:40Z</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>401816388</t>
+          <t>401816398</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
@@ -14337,12 +14389,12 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
@@ -14352,7 +14404,7 @@
       </c>
       <c r="I44" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J44" s="25" t="n">
@@ -14364,51 +14416,73 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-163</v>
+        <v>-182</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.549451</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.64539</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.600007</v>
+        <v>0.655325</v>
       </c>
       <c r="P44" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>-0.019765</v>
+        <v>0.009934999999999999</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="S44" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U44" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W44" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="X44" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y44" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="T44" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v2</t>
-        </is>
-      </c>
-      <c r="U44" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V44" s="24" t="n"/>
-      <c r="W44" s="26" t="n"/>
-      <c r="X44" s="26" t="n"/>
-      <c r="Y44" s="25" t="n"/>
-      <c r="Z44" s="26" t="n"/>
-      <c r="AA44" s="28" t="n"/>
-      <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="30" t="n"/>
-      <c r="AD44" s="24" t="n"/>
+      <c r="Z44" s="26" t="n">
+        <v>-182</v>
+      </c>
+      <c r="AA44" s="28" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AB44" s="28" t="n">
+        <v>-0.00039</v>
+      </c>
+      <c r="AC44" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:02.754328Z</t>
+        </is>
+      </c>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.10-4.32; raw selected-side p=0.6523, calibrated p=0.6000.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.22-4.93; raw selected-side p=0.7279, calibrated p=0.6553.</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -14418,7 +14492,7 @@
       </c>
       <c r="AG44" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH44" s="24" t="n"/>
@@ -14449,32 +14523,32 @@
       </c>
       <c r="AP44" s="24" t="inlineStr">
         <is>
-          <t>mlb-nym</t>
+          <t>mlb-sd</t>
         </is>
       </c>
       <c r="AQ44" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AR44" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AS44" s="24" t="inlineStr">
         <is>
-          <t>mlb-cle</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT44" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU44" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV44" s="24" t="n"/>
@@ -14492,7 +14566,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -14502,12 +14576,12 @@
       </c>
       <c r="BC44" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -14527,7 +14601,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -14539,21 +14613,25 @@
         <v>1.5</v>
       </c>
       <c r="BK44" s="26" t="n">
-        <v>-163</v>
+        <v>-182</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.549451</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.64539</v>
       </c>
       <c r="BN44" s="28" t="n">
-        <v>0.616915</v>
+        <v>0.641791</v>
       </c>
       <c r="BO44" s="28" t="n"/>
       <c r="BP44" s="25" t="n"/>
-      <c r="BQ44" s="27" t="n"/>
-      <c r="BR44" s="28" t="n"/>
+      <c r="BQ44" s="27" t="n">
+        <v>1.549451</v>
+      </c>
+      <c r="BR44" s="28" t="n">
+        <v>0.645</v>
+      </c>
       <c r="BS44" s="28" t="n"/>
       <c r="BT44" s="28" t="n"/>
       <c r="BU44" s="25" t="n"/>
@@ -14582,29 +14660,29 @@
       <c r="CR44" s="24" t="n"/>
       <c r="CS44" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>c7b77c0e4f0b4e4a</t>
+          <t>44764b238eb747c7</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-05T01:40Z</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>401816388</t>
+          <t>401816398</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
@@ -14614,12 +14692,12 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -14633,7 +14711,7 @@
         </is>
       </c>
       <c r="J45" s="25" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="K45" s="24" t="inlineStr">
         <is>
@@ -14641,51 +14719,73 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>-106</v>
+        <v>-117</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>1.943396</v>
+        <v>1.854701</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.514563</v>
+        <v>0.539171</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.521567</v>
+        <v>0.512594</v>
       </c>
       <c r="P45" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q45" s="28" t="n">
-        <v>0.007004</v>
+        <v>-0.026577</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="S45" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T45" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U45" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V45" s="24" t="n"/>
-      <c r="W45" s="26" t="n"/>
-      <c r="X45" s="26" t="n"/>
-      <c r="Y45" s="25" t="n"/>
-      <c r="Z45" s="26" t="n"/>
-      <c r="AA45" s="28" t="n"/>
-      <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="30" t="n"/>
-      <c r="AD45" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W45" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="X45" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y45" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z45" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA45" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB45" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC45" s="30" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="AD45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:03.225054Z</t>
+        </is>
+      </c>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.10-4.32; raw selected-side p=0.5399, calibrated p=0.5216.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.22-4.93; raw selected-side p=0.5273, calibrated p=0.5126.</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -14726,32 +14826,32 @@
       </c>
       <c r="AP45" s="24" t="inlineStr">
         <is>
-          <t>mlb-nym</t>
+          <t>mlb-sd</t>
         </is>
       </c>
       <c r="AQ45" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AR45" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AS45" s="24" t="inlineStr">
         <is>
-          <t>mlb-cle</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT45" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU45" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV45" s="24" t="n"/>
@@ -14769,7 +14869,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -14779,12 +14879,12 @@
       </c>
       <c r="BC45" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -14804,7 +14904,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -14813,24 +14913,28 @@
         </is>
       </c>
       <c r="BJ45" s="25" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK45" s="26" t="n">
-        <v>-106</v>
+        <v>-117</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>1.943396</v>
+        <v>1.854701</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.514563</v>
+        <v>0.539171</v>
       </c>
       <c r="BN45" s="28" t="n">
-        <v>0.5124379999999999</v>
+        <v>0.537313</v>
       </c>
       <c r="BO45" s="28" t="n"/>
       <c r="BP45" s="25" t="n"/>
-      <c r="BQ45" s="27" t="n"/>
-      <c r="BR45" s="28" t="n"/>
+      <c r="BQ45" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR45" s="28" t="n">
+        <v>0.54</v>
+      </c>
       <c r="BS45" s="28" t="n"/>
       <c r="BT45" s="28" t="n"/>
       <c r="BU45" s="25" t="n"/>
@@ -14859,29 +14963,29 @@
       <c r="CR45" s="24" t="n"/>
       <c r="CS45" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>d21c466f2c6e41c8</t>
+          <t>2a3c60fe55c84636</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T21:01:36.734850Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-05T23:30Z</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>401816390</t>
+          <t>401816408</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -14891,26 +14995,26 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I46" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J46" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="K46" s="24" t="inlineStr">
         <is>
@@ -14918,51 +15022,73 @@
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.440529</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.540597</v>
+        <v>0.527212</v>
       </c>
       <c r="P46" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q46" s="28" t="n">
-        <v>0.07976800000000001</v>
+        <v>0.086683</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S46" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U46" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V46" s="24" t="n"/>
-      <c r="W46" s="26" t="n"/>
-      <c r="X46" s="26" t="n"/>
-      <c r="Y46" s="25" t="n"/>
-      <c r="Z46" s="26" t="n"/>
-      <c r="AA46" s="28" t="n"/>
-      <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n"/>
-      <c r="AD46" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W46" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X46" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y46" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z46" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA46" s="28" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AB46" s="28" t="n">
+        <v>-0.000529</v>
+      </c>
+      <c r="AC46" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:25.925315Z</t>
+        </is>
+      </c>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.92-5.03; raw selected-side p=0.5618, calibrated p=0.5406.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.27-4.68; raw selected-side p=0.5862, calibrated p=0.5272.</t>
         </is>
       </c>
       <c r="AF46" s="31" t="inlineStr">
@@ -14972,7 +15098,7 @@
       </c>
       <c r="AG46" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH46" s="24" t="n"/>
@@ -15003,32 +15129,32 @@
       </c>
       <c r="AP46" s="24" t="inlineStr">
         <is>
-          <t>mlb-wsh</t>
+          <t>mlb-pit</t>
         </is>
       </c>
       <c r="AQ46" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AR46" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AS46" s="24" t="inlineStr">
         <is>
-          <t>mlb-phi</t>
+          <t>mlb-mil</t>
         </is>
       </c>
       <c r="AT46" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AU46" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AV46" s="24" t="n"/>
@@ -15046,7 +15172,7 @@
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
@@ -15056,12 +15182,12 @@
       </c>
       <c r="BC46" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
@@ -15081,7 +15207,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T21:01:36.734850Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -15090,24 +15216,28 @@
         </is>
       </c>
       <c r="BJ46" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK46" s="26" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.440529</v>
       </c>
       <c r="BN46" s="28" t="n">
-        <v>0.457711</v>
+        <v>0.437811</v>
       </c>
       <c r="BO46" s="28" t="n"/>
       <c r="BP46" s="25" t="n"/>
-      <c r="BQ46" s="27" t="n"/>
-      <c r="BR46" s="28" t="n"/>
+      <c r="BQ46" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BR46" s="28" t="n">
+        <v>0.44</v>
+      </c>
       <c r="BS46" s="28" t="n"/>
       <c r="BT46" s="28" t="n"/>
       <c r="BU46" s="25" t="n"/>
@@ -15143,22 +15273,22 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>24ac0a3e828e402a</t>
+          <t>277d52e1aa3241e2</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-07T21:56:47.081526Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-08T00:10Z</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>401816390</t>
+          <t>401816431</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -15168,26 +15298,26 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I47" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J47" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="K47" s="24" t="inlineStr">
         <is>
@@ -15195,51 +15325,73 @@
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>-117</v>
+        <v>-102</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.980392</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.50495</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.511059</v>
+        <v>0.658426</v>
       </c>
       <c r="P47" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q47" s="28" t="n">
-        <v>-0.028112</v>
+        <v>0.153476</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="S47" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U47" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V47" s="24" t="n"/>
-      <c r="W47" s="26" t="n"/>
-      <c r="X47" s="26" t="n"/>
-      <c r="Y47" s="25" t="n"/>
-      <c r="Z47" s="26" t="n"/>
-      <c r="AA47" s="28" t="n"/>
-      <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="30" t="n"/>
-      <c r="AD47" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W47" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="X47" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y47" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z47" s="26" t="n">
+        <v>-102</v>
+      </c>
+      <c r="AA47" s="28" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="AB47" s="28" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="AC47" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:03:10.114865Z</t>
+        </is>
+      </c>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.92-5.03; raw selected-side p=0.5091, calibrated p=0.5111.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.08-4.72; raw selected-side p=0.7325, calibrated p=0.6584.</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -15249,7 +15401,7 @@
       </c>
       <c r="AG47" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH47" s="24" t="n"/>
@@ -15280,32 +15432,32 @@
       </c>
       <c r="AP47" s="24" t="inlineStr">
         <is>
-          <t>mlb-wsh</t>
+          <t>mlb-chc</t>
         </is>
       </c>
       <c r="AQ47" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AR47" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AS47" s="24" t="inlineStr">
         <is>
-          <t>mlb-phi</t>
+          <t>mlb-kc</t>
         </is>
       </c>
       <c r="AT47" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AU47" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AV47" s="24" t="n"/>
@@ -15323,7 +15475,7 @@
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
@@ -15333,12 +15485,12 @@
       </c>
       <c r="BC47" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
@@ -15358,7 +15510,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-07T21:56:47.081526Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -15367,24 +15519,28 @@
         </is>
       </c>
       <c r="BJ47" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK47" s="26" t="n">
-        <v>-117</v>
+        <v>-102</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.980392</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.50495</v>
       </c>
       <c r="BN47" s="28" t="n">
-        <v>0.537313</v>
+        <v>0.502488</v>
       </c>
       <c r="BO47" s="28" t="n"/>
       <c r="BP47" s="25" t="n"/>
-      <c r="BQ47" s="27" t="n"/>
-      <c r="BR47" s="28" t="n"/>
+      <c r="BQ47" s="27" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="BR47" s="28" t="n">
+        <v>0.505</v>
+      </c>
       <c r="BS47" s="28" t="n"/>
       <c r="BT47" s="28" t="n"/>
       <c r="BU47" s="25" t="n"/>
@@ -15413,29 +15569,29 @@
       <c r="CR47" s="24" t="n"/>
       <c r="CS47" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>4269da3d4eca4177</t>
+          <t>9b3f4b2e5f574017</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-08T01:01:06.197155Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:05Z</t>
+          <t>2026-08-08T01:40Z</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>401816389</t>
+          <t>401816437</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
@@ -15445,12 +15601,12 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
@@ -15460,7 +15616,7 @@
       </c>
       <c r="I48" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J48" s="25" t="n">
@@ -15472,51 +15628,73 @@
         </is>
       </c>
       <c r="L48" s="26" t="n">
-        <v>-120</v>
+        <v>100</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>1.833333</v>
+        <v>2</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.5</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.612998</v>
+        <v>0.631578</v>
       </c>
       <c r="P48" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q48" s="28" t="n">
-        <v>0.06754300000000001</v>
+        <v>0.131578</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="S48" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U48" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V48" s="24" t="n"/>
-      <c r="W48" s="26" t="n"/>
-      <c r="X48" s="26" t="n"/>
-      <c r="Y48" s="25" t="n"/>
-      <c r="Z48" s="26" t="n"/>
-      <c r="AA48" s="28" t="n"/>
-      <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="30" t="n"/>
-      <c r="AD48" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W48" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X48" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y48" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z48" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA48" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB48" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:32:57.528646Z</t>
+        </is>
+      </c>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.35-4.35; raw selected-side p=0.6722, calibrated p=0.6130.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.62-4.87; raw selected-side p=0.6931, calibrated p=0.6316.</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
@@ -15557,32 +15735,32 @@
       </c>
       <c r="AP48" s="24" t="inlineStr">
         <is>
-          <t>mlb-stl</t>
+          <t>mlb-lad</t>
         </is>
       </c>
       <c r="AQ48" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AR48" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AS48" s="24" t="inlineStr">
         <is>
-          <t>mlb-nyy</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT48" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU48" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV48" s="24" t="n"/>
@@ -15600,7 +15778,7 @@
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
@@ -15610,12 +15788,12 @@
       </c>
       <c r="BC48" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
@@ -15635,7 +15813,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-08T01:01:06.197155Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -15647,21 +15825,25 @@
         <v>1.5</v>
       </c>
       <c r="BK48" s="26" t="n">
-        <v>-120</v>
+        <v>100</v>
       </c>
       <c r="BL48" s="27" t="n">
-        <v>1.833333</v>
+        <v>2</v>
       </c>
       <c r="BM48" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.5</v>
       </c>
       <c r="BN48" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.497512</v>
       </c>
       <c r="BO48" s="28" t="n"/>
       <c r="BP48" s="25" t="n"/>
-      <c r="BQ48" s="27" t="n"/>
-      <c r="BR48" s="28" t="n"/>
+      <c r="BQ48" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR48" s="28" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BS48" s="28" t="n"/>
       <c r="BT48" s="28" t="n"/>
       <c r="BU48" s="25" t="n"/>
@@ -15697,22 +15879,22 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>7447a7a90b074319</t>
+          <t>dd4b5a7fed1644da</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-09T17:06:46.891600Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:05Z</t>
+          <t>2026-08-09T18:10Z</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>401816389</t>
+          <t>401816461</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
@@ -15722,26 +15904,26 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I49" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J49" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="K49" s="24" t="inlineStr">
         <is>
@@ -15749,51 +15931,73 @@
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>-111</v>
+        <v>-102</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.980392</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.50495</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.510786</v>
+        <v>0.66173</v>
       </c>
       <c r="P49" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q49" s="28" t="n">
-        <v>-0.01528</v>
+        <v>0.15678</v>
       </c>
       <c r="R49" s="26" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="S49" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T49" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U49" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V49" s="24" t="n"/>
-      <c r="W49" s="26" t="n"/>
-      <c r="X49" s="26" t="n"/>
-      <c r="Y49" s="25" t="n"/>
-      <c r="Z49" s="26" t="n"/>
-      <c r="AA49" s="28" t="n"/>
-      <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="30" t="n"/>
-      <c r="AD49" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V49" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W49" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="X49" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y49" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z49" s="26" t="n">
+        <v>-102</v>
+      </c>
+      <c r="AA49" s="28" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="AB49" s="28" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="AC49" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T23:28:57.823411Z</t>
+        </is>
+      </c>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.35-4.35; raw selected-side p=0.5083, calibrated p=0.5108.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.78-4.36; raw selected-side p=0.7373, calibrated p=0.6617.</t>
         </is>
       </c>
       <c r="AF49" s="31" t="inlineStr">
@@ -15803,7 +16007,7 @@
       </c>
       <c r="AG49" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH49" s="24" t="n"/>
@@ -15834,32 +16038,32 @@
       </c>
       <c r="AP49" s="24" t="inlineStr">
         <is>
-          <t>mlb-stl</t>
+          <t>mlb-chc</t>
         </is>
       </c>
       <c r="AQ49" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AR49" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AS49" s="24" t="inlineStr">
         <is>
-          <t>mlb-nyy</t>
+          <t>mlb-kc</t>
         </is>
       </c>
       <c r="AT49" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AU49" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AV49" s="24" t="n"/>
@@ -15877,7 +16081,7 @@
       </c>
       <c r="BA49" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB49" s="24" t="inlineStr">
@@ -15887,12 +16091,12 @@
       </c>
       <c r="BC49" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD49" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE49" s="24" t="inlineStr">
@@ -15912,7 +16116,7 @@
       </c>
       <c r="BH49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-09T17:06:46.891600Z</t>
         </is>
       </c>
       <c r="BI49" s="24" t="inlineStr">
@@ -15921,24 +16125,28 @@
         </is>
       </c>
       <c r="BJ49" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK49" s="26" t="n">
-        <v>-111</v>
+        <v>-102</v>
       </c>
       <c r="BL49" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.980392</v>
       </c>
       <c r="BM49" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.50495</v>
       </c>
       <c r="BN49" s="28" t="n">
-        <v>0.522388</v>
+        <v>0.502488</v>
       </c>
       <c r="BO49" s="28" t="n"/>
       <c r="BP49" s="25" t="n"/>
-      <c r="BQ49" s="27" t="n"/>
-      <c r="BR49" s="28" t="n"/>
+      <c r="BQ49" s="27" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="BR49" s="28" t="n">
+        <v>0.505</v>
+      </c>
       <c r="BS49" s="28" t="n"/>
       <c r="BT49" s="28" t="n"/>
       <c r="BU49" s="25" t="n"/>
@@ -15967,29 +16175,29 @@
       <c r="CR49" s="24" t="n"/>
       <c r="CS49" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>74826e5d920a490b</t>
+          <t>d2207aef672c4f42</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-09T17:06:46.891600Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:10Z</t>
+          <t>2026-08-09T20:10Z</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>401816386</t>
+          <t>401816467</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
@@ -15999,12 +16207,12 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
@@ -16014,7 +16222,7 @@
       </c>
       <c r="I50" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J50" s="25" t="n">
@@ -16026,51 +16234,73 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>-174</v>
+        <v>-117</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>1.574713</v>
+        <v>1.854701</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.635036</v>
+        <v>0.539171</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.558902</v>
+        <v>0.63519</v>
       </c>
       <c r="P50" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q50" s="28" t="n">
-        <v>-0.07613399999999999</v>
+        <v>0.09601899999999999</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="S50" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T50" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U50" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V50" s="24" t="n"/>
-      <c r="W50" s="26" t="n"/>
-      <c r="X50" s="26" t="n"/>
-      <c r="Y50" s="25" t="n"/>
-      <c r="Z50" s="26" t="n"/>
-      <c r="AA50" s="28" t="n"/>
-      <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="30" t="n"/>
-      <c r="AD50" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V50" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W50" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X50" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y50" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z50" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA50" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB50" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC50" s="30" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="AD50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T23:28:58.193017Z</t>
+        </is>
+      </c>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.37-5.16; raw selected-side p=0.5897, calibrated p=0.5589.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.48-4.80; raw selected-side p=0.6984, calibrated p=0.6352.</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -16111,32 +16341,32 @@
       </c>
       <c r="AP50" s="24" t="inlineStr">
         <is>
-          <t>mlb-cws</t>
+          <t>mlb-lad</t>
         </is>
       </c>
       <c r="AQ50" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AR50" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AS50" s="24" t="inlineStr">
         <is>
-          <t>mlb-bos</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT50" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU50" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV50" s="24" t="n"/>
@@ -16154,7 +16384,7 @@
       </c>
       <c r="BA50" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB50" s="24" t="inlineStr">
@@ -16164,12 +16394,12 @@
       </c>
       <c r="BC50" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD50" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE50" s="24" t="inlineStr">
@@ -16189,7 +16419,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-09T17:06:46.891600Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -16201,21 +16431,25 @@
         <v>1.5</v>
       </c>
       <c r="BK50" s="26" t="n">
-        <v>-174</v>
+        <v>-117</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>1.574713</v>
+        <v>1.854701</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.635036</v>
+        <v>0.539171</v>
       </c>
       <c r="BN50" s="28" t="n">
-        <v>0.631841</v>
+        <v>0.537313</v>
       </c>
       <c r="BO50" s="28" t="n"/>
       <c r="BP50" s="25" t="n"/>
-      <c r="BQ50" s="27" t="n"/>
-      <c r="BR50" s="28" t="n"/>
+      <c r="BQ50" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR50" s="28" t="n">
+        <v>0.54</v>
+      </c>
       <c r="BS50" s="28" t="n"/>
       <c r="BT50" s="28" t="n"/>
       <c r="BU50" s="25" t="n"/>
@@ -16244,29 +16478,29 @@
       <c r="CR50" s="24" t="n"/>
       <c r="CS50" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>8e58043a780a4849</t>
+          <t>1ce29fb29b204ce1</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-09T23:32:16.171272Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:10Z</t>
+          <t>2026-08-10T00:20Z</t>
         </is>
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>401816386</t>
+          <t>401816466</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -16276,26 +16510,26 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I51" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J51" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="K51" s="24" t="inlineStr">
         <is>
@@ -16303,51 +16537,73 @@
         </is>
       </c>
       <c r="L51" s="26" t="n">
-        <v>-122</v>
+        <v>-178</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.561798</v>
       </c>
       <c r="N51" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.640288</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.529648</v>
+        <v>0.5895359999999999</v>
       </c>
       <c r="P51" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q51" s="28" t="n">
-        <v>-0.019902</v>
+        <v>-0.050752</v>
       </c>
       <c r="R51" s="26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S51" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U51" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V51" s="24" t="n"/>
-      <c r="W51" s="26" t="n"/>
-      <c r="X51" s="26" t="n"/>
-      <c r="Y51" s="25" t="n"/>
-      <c r="Z51" s="26" t="n"/>
-      <c r="AA51" s="28" t="n"/>
-      <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="30" t="n"/>
-      <c r="AD51" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W51" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X51" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y51" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z51" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="AA51" s="28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB51" s="28" t="n">
+        <v>-0.000288</v>
+      </c>
+      <c r="AC51" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:37:28.508521Z</t>
+        </is>
+      </c>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.37-5.16; raw selected-side p=0.5635, calibrated p=0.5296.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.24-4.65; raw selected-side p=0.6314, calibrated p=0.5895.</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -16357,7 +16613,7 @@
       </c>
       <c r="AG51" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH51" s="24" t="n"/>
@@ -16388,32 +16644,32 @@
       </c>
       <c r="AP51" s="24" t="inlineStr">
         <is>
-          <t>mlb-cws</t>
+          <t>mlb-hou</t>
         </is>
       </c>
       <c r="AQ51" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AR51" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AS51" s="24" t="inlineStr">
         <is>
-          <t>mlb-bos</t>
+          <t>mlb-sd</t>
         </is>
       </c>
       <c r="AT51" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AU51" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AV51" s="24" t="n"/>
@@ -16431,7 +16687,7 @@
       </c>
       <c r="BA51" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB51" s="24" t="inlineStr">
@@ -16441,12 +16697,12 @@
       </c>
       <c r="BC51" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD51" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE51" s="24" t="inlineStr">
@@ -16466,7 +16722,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-09T23:32:16.171272Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -16475,24 +16731,28 @@
         </is>
       </c>
       <c r="BJ51" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK51" s="26" t="n">
-        <v>-122</v>
+        <v>-178</v>
       </c>
       <c r="BL51" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.561798</v>
       </c>
       <c r="BM51" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.640288</v>
       </c>
       <c r="BN51" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.636816</v>
       </c>
       <c r="BO51" s="28" t="n"/>
       <c r="BP51" s="25" t="n"/>
-      <c r="BQ51" s="27" t="n"/>
-      <c r="BR51" s="28" t="n"/>
+      <c r="BQ51" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BR51" s="28" t="n">
+        <v>0.64</v>
+      </c>
       <c r="BS51" s="28" t="n"/>
       <c r="BT51" s="28" t="n"/>
       <c r="BU51" s="25" t="n"/>
@@ -16528,22 +16788,22 @@
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>8c1d1d3f571d4025</t>
+          <t>5b674284b4144ae4</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-09T23:32:16.171272Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:15Z</t>
+          <t>2026-08-10T00:20Z</t>
         </is>
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>401816387</t>
+          <t>401816466</t>
         </is>
       </c>
       <c r="E52" s="24" t="inlineStr">
@@ -16553,26 +16813,26 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I52" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J52" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="K52" s="24" t="inlineStr">
         <is>
@@ -16580,51 +16840,73 @@
         </is>
       </c>
       <c r="L52" s="26" t="n">
-        <v>-150</v>
+        <v>-125</v>
       </c>
       <c r="M52" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.8</v>
       </c>
       <c r="N52" s="28" t="n">
-        <v>0.6</v>
+        <v>0.555556</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>0.567661</v>
+        <v>0.5072410000000001</v>
       </c>
       <c r="P52" s="28" t="n">
-        <v>0.042131</v>
+        <v>0.05172</v>
       </c>
       <c r="Q52" s="28" t="n">
-        <v>-0.032339</v>
+        <v>-0.048315</v>
       </c>
       <c r="R52" s="26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S52" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T52" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U52" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V52" s="24" t="n"/>
-      <c r="W52" s="26" t="n"/>
-      <c r="X52" s="26" t="n"/>
-      <c r="Y52" s="25" t="n"/>
-      <c r="Z52" s="26" t="n"/>
-      <c r="AA52" s="28" t="n"/>
-      <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n"/>
-      <c r="AD52" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W52" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X52" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y52" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z52" s="26" t="n">
+        <v>-125</v>
+      </c>
+      <c r="AA52" s="28" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AB52" s="28" t="n">
+        <v>-0.000556</v>
+      </c>
+      <c r="AC52" s="30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:37:28.912292Z</t>
+        </is>
+      </c>
       <c r="AE52" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.10-4.82; raw selected-side p=0.6030, calibrated p=0.5677.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.24-4.65; raw selected-side p=0.5058, calibrated p=0.5072.</t>
         </is>
       </c>
       <c r="AF52" s="31" t="inlineStr">
@@ -16665,32 +16947,32 @@
       </c>
       <c r="AP52" s="24" t="inlineStr">
         <is>
-          <t>mlb-mia</t>
+          <t>mlb-hou</t>
         </is>
       </c>
       <c r="AQ52" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AR52" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AS52" s="24" t="inlineStr">
         <is>
-          <t>mlb-atl</t>
+          <t>mlb-sd</t>
         </is>
       </c>
       <c r="AT52" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AU52" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AV52" s="24" t="n"/>
@@ -16708,7 +16990,7 @@
       </c>
       <c r="BA52" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB52" s="24" t="inlineStr">
@@ -16718,12 +17000,12 @@
       </c>
       <c r="BC52" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD52" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE52" s="24" t="inlineStr">
@@ -16743,7 +17025,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-09T23:32:16.171272Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -16752,24 +17034,28 @@
         </is>
       </c>
       <c r="BJ52" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK52" s="26" t="n">
-        <v>-150</v>
+        <v>-125</v>
       </c>
       <c r="BL52" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.8</v>
       </c>
       <c r="BM52" s="28" t="n">
-        <v>0.6</v>
+        <v>0.555556</v>
       </c>
       <c r="BN52" s="28" t="n">
-        <v>0.597015</v>
+        <v>0.552239</v>
       </c>
       <c r="BO52" s="28" t="n"/>
       <c r="BP52" s="25" t="n"/>
-      <c r="BQ52" s="27" t="n"/>
-      <c r="BR52" s="28" t="n"/>
+      <c r="BQ52" s="27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR52" s="28" t="n">
+        <v>0.555</v>
+      </c>
       <c r="BS52" s="28" t="n"/>
       <c r="BT52" s="28" t="n"/>
       <c r="BU52" s="25" t="n"/>
@@ -16805,22 +17091,22 @@
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>1f9fb77aaf164589</t>
+          <t>dd6c65cefda246bb</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:34:47.251195Z</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:15Z</t>
+          <t>2026-08-10T21:40:00-0400</t>
         </is>
       </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
-          <t>401816387</t>
+          <t>401816473</t>
         </is>
       </c>
       <c r="E53" s="24" t="inlineStr">
@@ -16830,59 +17116,55 @@
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="G53" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I53" s="24" t="inlineStr">
         <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J53" s="25" t="n">
-        <v>9.5</v>
-      </c>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J53" s="25" t="n"/>
       <c r="K53" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L53" s="26" t="n">
-        <v>-113</v>
+        <v>-186</v>
       </c>
       <c r="M53" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.537634</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.65035</v>
       </c>
       <c r="O53" s="28" t="n">
-        <v>0.54376</v>
-      </c>
-      <c r="P53" s="28" t="n">
-        <v>0.042131</v>
-      </c>
+        <v>0.651088</v>
+      </c>
+      <c r="P53" s="28" t="n"/>
       <c r="Q53" s="28" t="n">
-        <v>0.013244</v>
+        <v>0.000738</v>
       </c>
       <c r="R53" s="26" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="S53" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T53" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U53" s="24" t="inlineStr">
@@ -16901,12 +17183,12 @@
       <c r="AD53" s="24" t="n"/>
       <c r="AE53" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.10-4.82; raw selected-side p=0.6048, calibrated p=0.5438.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.6500 (aec-mlb-col-az-2026-08-10); model edge vs ask +0.0011.</t>
         </is>
       </c>
       <c r="AF53" s="31" t="inlineStr">
         <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+          <t>Learned model; shadow-qualified via operator override.</t>
         </is>
       </c>
       <c r="AG53" s="24" t="inlineStr">
@@ -16942,32 +17224,32 @@
       </c>
       <c r="AP53" s="24" t="inlineStr">
         <is>
-          <t>mlb-mia</t>
+          <t>mlb-col</t>
         </is>
       </c>
       <c r="AQ53" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AR53" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AS53" s="24" t="inlineStr">
         <is>
-          <t>mlb-atl</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT53" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU53" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV53" s="24" t="n"/>
@@ -16980,32 +17262,32 @@
       <c r="AY53" s="24" t="n"/>
       <c r="AZ53" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA53" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB53" s="24" t="inlineStr">
         <is>
-          <t>flat_probability_shrinkage_toward_half</t>
+          <t>learned_lr</t>
         </is>
       </c>
       <c r="BC53" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD53" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE53" s="24" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>b4a698ea92aeb5d0</t>
         </is>
       </c>
       <c r="BF53" s="24" t="inlineStr">
@@ -17015,12 +17297,12 @@
       </c>
       <c r="BG53" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-paired-v1</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:34:11.790019Z</t>
         </is>
       </c>
       <c r="BI53" s="24" t="inlineStr">
@@ -17028,20 +17310,18 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ53" s="25" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="BJ53" s="25" t="n"/>
       <c r="BK53" s="26" t="n">
-        <v>-113</v>
+        <v>-186</v>
       </c>
       <c r="BL53" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.537634</v>
       </c>
       <c r="BM53" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.65035</v>
       </c>
       <c r="BN53" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.646766</v>
       </c>
       <c r="BO53" s="28" t="n"/>
       <c r="BP53" s="25" t="n"/>
@@ -17057,22 +17337,54 @@
       <c r="BZ53" s="24" t="n"/>
       <c r="CA53" s="31" t="n"/>
       <c r="CB53" s="24" t="n"/>
-      <c r="CC53" s="24" t="n"/>
-      <c r="CD53" s="24" t="n"/>
-      <c r="CE53" s="24" t="n"/>
-      <c r="CF53" s="24" t="n"/>
+      <c r="CC53" s="24" t="inlineStr">
+        <is>
+          <t>0.6941730683</t>
+        </is>
+      </c>
+      <c r="CD53" s="24" t="inlineStr">
+        <is>
+          <t>-0.291055</t>
+        </is>
+      </c>
+      <c r="CE53" s="24" t="inlineStr">
+        <is>
+          <t>1.097</t>
+        </is>
+      </c>
+      <c r="CF53" s="24" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="CG53" s="24" t="n"/>
       <c r="CH53" s="24" t="n"/>
       <c r="CI53" s="24" t="n"/>
-      <c r="CJ53" s="24" t="n"/>
+      <c r="CJ53" s="24" t="inlineStr">
+        <is>
+          <t>1.199176</t>
+        </is>
+      </c>
       <c r="CK53" s="24" t="n"/>
-      <c r="CL53" s="24" t="n"/>
-      <c r="CM53" s="24" t="n"/>
+      <c r="CL53" s="24" t="inlineStr">
+        <is>
+          <t>0.159831</t>
+        </is>
+      </c>
+      <c r="CM53" s="24" t="inlineStr">
+        <is>
+          <t>-2.7333</t>
+        </is>
+      </c>
       <c r="CN53" s="24" t="n"/>
       <c r="CO53" s="24" t="n"/>
       <c r="CP53" s="24" t="n"/>
       <c r="CQ53" s="24" t="n"/>
-      <c r="CR53" s="24" t="n"/>
+      <c r="CR53" s="24" t="inlineStr">
+        <is>
+          <t>0.651088</t>
+        </is>
+      </c>
       <c r="CS53" s="24" t="inlineStr">
         <is>
           <t>True</t>
@@ -17082,22 +17394,22 @@
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>032ac8c42bb54932</t>
+          <t>4569f4acab14488c</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:34:47.251195Z</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:40Z</t>
+          <t>2026-08-10T22:10:00-0400</t>
         </is>
       </c>
       <c r="D54" s="24" t="inlineStr">
         <is>
-          <t>401816392</t>
+          <t>401816475</t>
         </is>
       </c>
       <c r="E54" s="24" t="inlineStr">
@@ -17107,17 +17419,17 @@
       </c>
       <c r="F54" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="G54" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="H54" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I54" s="24" t="inlineStr">
@@ -17125,41 +17437,37 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J54" s="25" t="n">
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>-251</v>
+      </c>
+      <c r="M54" s="27" t="n">
+        <v>1.398406</v>
+      </c>
+      <c r="N54" s="28" t="n">
+        <v>0.7151</v>
+      </c>
+      <c r="O54" s="28" t="n">
+        <v>0.634885</v>
+      </c>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="28" t="n">
+        <v>-0.08021499999999999</v>
+      </c>
+      <c r="R54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="29" t="n">
         <v>1.5</v>
       </c>
-      <c r="K54" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L54" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M54" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N54" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O54" s="28" t="n">
-        <v>0.700193</v>
-      </c>
-      <c r="P54" s="28" t="n">
-        <v>0.05172</v>
-      </c>
-      <c r="Q54" s="28" t="n">
-        <v>0.150643</v>
-      </c>
-      <c r="R54" s="26" t="n">
-        <v>95</v>
-      </c>
-      <c r="S54" s="29" t="n">
-        <v>2</v>
-      </c>
       <c r="T54" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U54" s="24" t="inlineStr">
@@ -17178,12 +17486,12 @@
       <c r="AD54" s="24" t="n"/>
       <c r="AE54" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.16-4.32; raw selected-side p=0.8051, calibrated p=0.7002.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.7150 (aec-mlb-kc-lad-2026-08-10); model edge vs ask -0.0801.</t>
         </is>
       </c>
       <c r="AF54" s="31" t="inlineStr">
         <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+          <t>Learned model; shadow-qualified via operator override.</t>
         </is>
       </c>
       <c r="AG54" s="24" t="inlineStr">
@@ -17219,32 +17527,32 @@
       </c>
       <c r="AP54" s="24" t="inlineStr">
         <is>
-          <t>mlb-min</t>
+          <t>mlb-kc</t>
         </is>
       </c>
       <c r="AQ54" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AR54" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AS54" s="24" t="inlineStr">
         <is>
-          <t>mlb-kc</t>
+          <t>mlb-lad</t>
         </is>
       </c>
       <c r="AT54" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AU54" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AV54" s="24" t="n"/>
@@ -17257,32 +17565,32 @@
       <c r="AY54" s="24" t="n"/>
       <c r="AZ54" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA54" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BB54" s="24" t="inlineStr">
         <is>
-          <t>flat_probability_shrinkage_toward_half</t>
+          <t>learned_lr</t>
         </is>
       </c>
       <c r="BC54" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD54" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
         </is>
       </c>
       <c r="BE54" s="24" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>19d07a09c729d869</t>
         </is>
       </c>
       <c r="BF54" s="24" t="inlineStr">
@@ -17292,12 +17600,12 @@
       </c>
       <c r="BG54" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-paired-v1</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:34:13.862219Z</t>
         </is>
       </c>
       <c r="BI54" s="24" t="inlineStr">
@@ -17305,20 +17613,18 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ54" s="25" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="BJ54" s="25" t="n"/>
       <c r="BK54" s="26" t="n">
-        <v>-122</v>
+        <v>-251</v>
       </c>
       <c r="BL54" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.398406</v>
       </c>
       <c r="BM54" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.7151</v>
       </c>
       <c r="BN54" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.711443</v>
       </c>
       <c r="BO54" s="28" t="n"/>
       <c r="BP54" s="25" t="n"/>
@@ -17334,47 +17640,79 @@
       <c r="BZ54" s="24" t="n"/>
       <c r="CA54" s="31" t="n"/>
       <c r="CB54" s="24" t="n"/>
-      <c r="CC54" s="24" t="n"/>
-      <c r="CD54" s="24" t="n"/>
-      <c r="CE54" s="24" t="n"/>
-      <c r="CF54" s="24" t="n"/>
+      <c r="CC54" s="24" t="inlineStr">
+        <is>
+          <t>0.6689872193</t>
+        </is>
+      </c>
+      <c r="CD54" s="24" t="inlineStr">
+        <is>
+          <t>-0.660466</t>
+        </is>
+      </c>
+      <c r="CE54" s="24" t="inlineStr">
+        <is>
+          <t>1.026</t>
+        </is>
+      </c>
+      <c r="CF54" s="24" t="inlineStr">
+        <is>
+          <t>1.0042</t>
+        </is>
+      </c>
       <c r="CG54" s="24" t="n"/>
       <c r="CH54" s="24" t="n"/>
       <c r="CI54" s="24" t="n"/>
-      <c r="CJ54" s="24" t="n"/>
+      <c r="CJ54" s="24" t="inlineStr">
+        <is>
+          <t>-0.432411</t>
+        </is>
+      </c>
       <c r="CK54" s="24" t="n"/>
-      <c r="CL54" s="24" t="n"/>
-      <c r="CM54" s="24" t="n"/>
+      <c r="CL54" s="24" t="inlineStr">
+        <is>
+          <t>-0.485019</t>
+        </is>
+      </c>
+      <c r="CM54" s="24" t="inlineStr">
+        <is>
+          <t>-4.417</t>
+        </is>
+      </c>
       <c r="CN54" s="24" t="n"/>
       <c r="CO54" s="24" t="n"/>
       <c r="CP54" s="24" t="n"/>
       <c r="CQ54" s="24" t="n"/>
-      <c r="CR54" s="24" t="n"/>
+      <c r="CR54" s="24" t="inlineStr">
+        <is>
+          <t>0.634885</t>
+        </is>
+      </c>
       <c r="CS54" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>352ff4cb49064cdb</t>
+          <t>1a685892bc8d4f32</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:40Z</t>
+          <t>2026-08-10T23:07Z</t>
         </is>
       </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
-          <t>401816392</t>
+          <t>401816469</t>
         </is>
       </c>
       <c r="E55" s="24" t="inlineStr">
@@ -17384,26 +17722,26 @@
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="G55" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="H55" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I55" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J55" s="25" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="K55" s="24" t="inlineStr">
         <is>
@@ -17420,23 +17758,23 @@
         <v>0.545455</v>
       </c>
       <c r="O55" s="28" t="n">
-        <v>0.587703</v>
+        <v>0.557987</v>
       </c>
       <c r="P55" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q55" s="28" t="n">
-        <v>0.042248</v>
+        <v>0.012532</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="S55" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T55" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U55" s="24" t="inlineStr">
@@ -17455,7 +17793,7 @@
       <c r="AD55" s="24" t="n"/>
       <c r="AE55" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.16-4.32; raw selected-side p=0.7334, calibrated p=0.5877.</t>
+          <t>Measured Edge Margin: Trend Engine projected 5.15-4.30; raw selected-side p=0.5851, calibrated p=0.5580.</t>
         </is>
       </c>
       <c r="AF55" s="31" t="inlineStr">
@@ -17496,32 +17834,32 @@
       </c>
       <c r="AP55" s="24" t="inlineStr">
         <is>
-          <t>mlb-min</t>
+          <t>mlb-bos</t>
         </is>
       </c>
       <c r="AQ55" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AR55" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AS55" s="24" t="inlineStr">
         <is>
-          <t>mlb-kc</t>
+          <t>mlb-tor</t>
         </is>
       </c>
       <c r="AT55" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AU55" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AV55" s="24" t="n"/>
@@ -17539,7 +17877,7 @@
       </c>
       <c r="BA55" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB55" s="24" t="inlineStr">
@@ -17549,12 +17887,12 @@
       </c>
       <c r="BC55" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD55" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE55" s="24" t="inlineStr">
@@ -17574,7 +17912,7 @@
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -17583,7 +17921,7 @@
         </is>
       </c>
       <c r="BJ55" s="25" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK55" s="26" t="n">
         <v>-120</v>
@@ -17636,22 +17974,22 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>72db7fcab77e4e00</t>
+          <t>00829b16f9304859</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:40Z</t>
+          <t>2026-08-10T23:07Z</t>
         </is>
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>401816393</t>
+          <t>401816469</t>
         </is>
       </c>
       <c r="E56" s="24" t="inlineStr">
@@ -17661,26 +17999,26 @@
       </c>
       <c r="F56" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="G56" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="H56" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I56" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J56" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="K56" s="24" t="inlineStr">
         <is>
@@ -17688,32 +18026,32 @@
         </is>
       </c>
       <c r="L56" s="26" t="n">
-        <v>-147</v>
+        <v>106</v>
       </c>
       <c r="M56" s="27" t="n">
-        <v>1.680272</v>
+        <v>2.06</v>
       </c>
       <c r="N56" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.485437</v>
       </c>
       <c r="O56" s="28" t="n">
-        <v>0.597054</v>
+        <v>0.520282</v>
       </c>
       <c r="P56" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q56" s="28" t="n">
-        <v>0.001912</v>
+        <v>0.034845</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="S56" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T56" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U56" s="24" t="inlineStr">
@@ -17732,7 +18070,7 @@
       <c r="AD56" s="24" t="n"/>
       <c r="AE56" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.58-4.00; raw selected-side p=0.6479, calibrated p=0.5971.</t>
+          <t>Measured Edge Totals: Trend Engine projected 5.15-4.30; raw selected-side p=0.5583, calibrated p=0.5203.</t>
         </is>
       </c>
       <c r="AF56" s="31" t="inlineStr">
@@ -17773,32 +18111,32 @@
       </c>
       <c r="AP56" s="24" t="inlineStr">
         <is>
-          <t>mlb-pit</t>
+          <t>mlb-bos</t>
         </is>
       </c>
       <c r="AQ56" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AR56" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AS56" s="24" t="inlineStr">
         <is>
-          <t>mlb-mil</t>
+          <t>mlb-tor</t>
         </is>
       </c>
       <c r="AT56" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AU56" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AV56" s="24" t="n"/>
@@ -17816,7 +18154,7 @@
       </c>
       <c r="BA56" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB56" s="24" t="inlineStr">
@@ -17826,12 +18164,12 @@
       </c>
       <c r="BC56" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD56" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE56" s="24" t="inlineStr">
@@ -17851,7 +18189,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -17860,19 +18198,19 @@
         </is>
       </c>
       <c r="BJ56" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK56" s="26" t="n">
-        <v>-147</v>
+        <v>106</v>
       </c>
       <c r="BL56" s="27" t="n">
-        <v>1.680272</v>
+        <v>2.06</v>
       </c>
       <c r="BM56" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.485437</v>
       </c>
       <c r="BN56" s="28" t="n">
-        <v>0.59204</v>
+        <v>0.482587</v>
       </c>
       <c r="BO56" s="28" t="n"/>
       <c r="BP56" s="25" t="n"/>
@@ -17913,22 +18251,22 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>3aaaf6eb6eef4eb1</t>
+          <t>620d1a1a74724f8f</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:40Z</t>
+          <t>2026-08-10T23:15Z</t>
         </is>
       </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
-          <t>401816393</t>
+          <t>401816470</t>
         </is>
       </c>
       <c r="E57" s="24" t="inlineStr">
@@ -17938,26 +18276,26 @@
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="G57" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="H57" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I57" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J57" s="25" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="K57" s="24" t="inlineStr">
         <is>
@@ -17965,32 +18303,32 @@
         </is>
       </c>
       <c r="L57" s="26" t="n">
-        <v>-106</v>
+        <v>-150</v>
       </c>
       <c r="M57" s="27" t="n">
-        <v>1.943396</v>
+        <v>1.666667</v>
       </c>
       <c r="N57" s="28" t="n">
-        <v>0.514563</v>
+        <v>0.6</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>0.523429</v>
+        <v>0.619313</v>
       </c>
       <c r="P57" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q57" s="28" t="n">
-        <v>0.008866000000000001</v>
+        <v>0.019313</v>
       </c>
       <c r="R57" s="26" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="S57" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T57" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U57" s="24" t="inlineStr">
@@ -18009,7 +18347,7 @@
       <c r="AD57" s="24" t="n"/>
       <c r="AE57" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.58-4.00; raw selected-side p=0.5453, calibrated p=0.5234.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.23-4.22; raw selected-side p=0.6751, calibrated p=0.6193.</t>
         </is>
       </c>
       <c r="AF57" s="31" t="inlineStr">
@@ -18050,32 +18388,32 @@
       </c>
       <c r="AP57" s="24" t="inlineStr">
         <is>
-          <t>mlb-pit</t>
+          <t>mlb-nym</t>
         </is>
       </c>
       <c r="AQ57" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AR57" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AS57" s="24" t="inlineStr">
         <is>
-          <t>mlb-mil</t>
+          <t>mlb-atl</t>
         </is>
       </c>
       <c r="AT57" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AU57" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AV57" s="24" t="n"/>
@@ -18093,7 +18431,7 @@
       </c>
       <c r="BA57" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB57" s="24" t="inlineStr">
@@ -18103,12 +18441,12 @@
       </c>
       <c r="BC57" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD57" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE57" s="24" t="inlineStr">
@@ -18128,7 +18466,7 @@
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -18137,19 +18475,19 @@
         </is>
       </c>
       <c r="BJ57" s="25" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK57" s="26" t="n">
-        <v>-106</v>
+        <v>-150</v>
       </c>
       <c r="BL57" s="27" t="n">
-        <v>1.943396</v>
+        <v>1.666667</v>
       </c>
       <c r="BM57" s="28" t="n">
-        <v>0.514563</v>
+        <v>0.6</v>
       </c>
       <c r="BN57" s="28" t="n">
-        <v>0.509901</v>
+        <v>0.597015</v>
       </c>
       <c r="BO57" s="28" t="n"/>
       <c r="BP57" s="25" t="n"/>
@@ -18190,22 +18528,22 @@
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>efd57fffe90f4d98</t>
+          <t>159cc49b92fe48a8</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:05Z</t>
+          <t>2026-08-10T23:15Z</t>
         </is>
       </c>
       <c r="D58" s="24" t="inlineStr">
         <is>
-          <t>401816391</t>
+          <t>401816470</t>
         </is>
       </c>
       <c r="E58" s="24" t="inlineStr">
@@ -18215,26 +18553,26 @@
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="G58" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="H58" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I58" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J58" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="K58" s="24" t="inlineStr">
         <is>
@@ -18242,32 +18580,32 @@
         </is>
       </c>
       <c r="L58" s="26" t="n">
-        <v>117</v>
+        <v>-104</v>
       </c>
       <c r="M58" s="27" t="n">
-        <v>2.17</v>
+        <v>1.961538</v>
       </c>
       <c r="N58" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.509804</v>
       </c>
       <c r="O58" s="28" t="n">
-        <v>0.62835</v>
+        <v>0.514954</v>
       </c>
       <c r="P58" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q58" s="28" t="n">
-        <v>0.167521</v>
+        <v>0.00515</v>
       </c>
       <c r="R58" s="26" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="S58" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T58" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U58" s="24" t="inlineStr">
@@ -18286,7 +18624,7 @@
       <c r="AD58" s="24" t="n"/>
       <c r="AE58" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.82-3.91; raw selected-side p=0.6956, calibrated p=0.6284.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.23-4.22; raw selected-side p=0.5369, calibrated p=0.5150.</t>
         </is>
       </c>
       <c r="AF58" s="31" t="inlineStr">
@@ -18327,32 +18665,32 @@
       </c>
       <c r="AP58" s="24" t="inlineStr">
         <is>
-          <t>mlb-lad</t>
+          <t>mlb-nym</t>
         </is>
       </c>
       <c r="AQ58" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AR58" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AS58" s="24" t="inlineStr">
         <is>
-          <t>mlb-chc</t>
+          <t>mlb-atl</t>
         </is>
       </c>
       <c r="AT58" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AU58" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AV58" s="24" t="n"/>
@@ -18370,7 +18708,7 @@
       </c>
       <c r="BA58" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB58" s="24" t="inlineStr">
@@ -18380,12 +18718,12 @@
       </c>
       <c r="BC58" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD58" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE58" s="24" t="inlineStr">
@@ -18405,7 +18743,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -18414,19 +18752,19 @@
         </is>
       </c>
       <c r="BJ58" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK58" s="26" t="n">
-        <v>117</v>
+        <v>-104</v>
       </c>
       <c r="BL58" s="27" t="n">
-        <v>2.17</v>
+        <v>1.961538</v>
       </c>
       <c r="BM58" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.509804</v>
       </c>
       <c r="BN58" s="28" t="n">
-        <v>0.455446</v>
+        <v>0.507463</v>
       </c>
       <c r="BO58" s="28" t="n"/>
       <c r="BP58" s="25" t="n"/>
@@ -18467,22 +18805,22 @@
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>5afdfe6a6e5342e0</t>
+          <t>6ffd04e822644064</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:05Z</t>
+          <t>2026-08-10T23:40Z</t>
         </is>
       </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
-          <t>401816391</t>
+          <t>401816471</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
@@ -18492,26 +18830,26 @@
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="G59" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I59" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J59" s="25" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="K59" s="24" t="inlineStr">
         <is>
@@ -18519,32 +18857,32 @@
         </is>
       </c>
       <c r="L59" s="26" t="n">
-        <v>-122</v>
+        <v>-156</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.641026</v>
       </c>
       <c r="N59" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.609375</v>
       </c>
       <c r="O59" s="28" t="n">
-        <v>0.579434</v>
+        <v>0.581972</v>
       </c>
       <c r="P59" s="28" t="n">
-        <v>0.042131</v>
+        <v>0.05172</v>
       </c>
       <c r="Q59" s="28" t="n">
-        <v>0.029884</v>
+        <v>-0.027403</v>
       </c>
       <c r="R59" s="26" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="S59" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T59" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U59" s="24" t="inlineStr">
@@ -18563,7 +18901,7 @@
       <c r="AD59" s="24" t="n"/>
       <c r="AE59" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.82-3.91; raw selected-side p=0.7092, calibrated p=0.5794.</t>
+          <t>Measured Edge Margin: Trend Engine projected 5.02-4.58; raw selected-side p=0.6203, calibrated p=0.5820.</t>
         </is>
       </c>
       <c r="AF59" s="31" t="inlineStr">
@@ -18604,32 +18942,32 @@
       </c>
       <c r="AP59" s="24" t="inlineStr">
         <is>
-          <t>mlb-lad</t>
+          <t>mlb-bal</t>
         </is>
       </c>
       <c r="AQ59" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AR59" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AS59" s="24" t="inlineStr">
         <is>
-          <t>mlb-chc</t>
+          <t>mlb-min</t>
         </is>
       </c>
       <c r="AT59" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AU59" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AV59" s="24" t="n"/>
@@ -18647,7 +18985,7 @@
       </c>
       <c r="BA59" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB59" s="24" t="inlineStr">
@@ -18657,12 +18995,12 @@
       </c>
       <c r="BC59" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD59" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE59" s="24" t="inlineStr">
@@ -18682,7 +19020,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -18691,19 +19029,19 @@
         </is>
       </c>
       <c r="BJ59" s="25" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK59" s="26" t="n">
-        <v>-122</v>
+        <v>-156</v>
       </c>
       <c r="BL59" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.641026</v>
       </c>
       <c r="BM59" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.609375</v>
       </c>
       <c r="BN59" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.606965</v>
       </c>
       <c r="BO59" s="28" t="n"/>
       <c r="BP59" s="25" t="n"/>
@@ -18737,29 +19075,29 @@
       <c r="CR59" s="24" t="n"/>
       <c r="CS59" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>19c2aae4fb7046a6</t>
+          <t>9a74e7c2c6f64669</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:05Z</t>
+          <t>2026-08-10T23:40Z</t>
         </is>
       </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
-          <t>401816394</t>
+          <t>401816471</t>
         </is>
       </c>
       <c r="E60" s="24" t="inlineStr">
@@ -18769,26 +19107,26 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="G60" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I60" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J60" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="K60" s="24" t="inlineStr">
         <is>
@@ -18796,32 +19134,32 @@
         </is>
       </c>
       <c r="L60" s="26" t="n">
-        <v>-120</v>
+        <v>102</v>
       </c>
       <c r="M60" s="27" t="n">
-        <v>1.833333</v>
+        <v>2.02</v>
       </c>
       <c r="N60" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.49505</v>
       </c>
       <c r="O60" s="28" t="n">
-        <v>0.657612</v>
+        <v>0.522406</v>
       </c>
       <c r="P60" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q60" s="28" t="n">
-        <v>0.112157</v>
+        <v>0.027356</v>
       </c>
       <c r="R60" s="26" t="n">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="S60" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T60" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U60" s="24" t="inlineStr">
@@ -18840,7 +19178,7 @@
       <c r="AD60" s="24" t="n"/>
       <c r="AE60" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.98-4.16; raw selected-side p=0.7401, calibrated p=0.6576.</t>
+          <t>Measured Edge Totals: Trend Engine projected 5.02-4.58; raw selected-side p=0.5668, calibrated p=0.5224.</t>
         </is>
       </c>
       <c r="AF60" s="31" t="inlineStr">
@@ -18881,32 +19219,32 @@
       </c>
       <c r="AP60" s="24" t="inlineStr">
         <is>
-          <t>mlb-sf</t>
+          <t>mlb-bal</t>
         </is>
       </c>
       <c r="AQ60" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AR60" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AS60" s="24" t="inlineStr">
         <is>
-          <t>mlb-tex</t>
+          <t>mlb-min</t>
         </is>
       </c>
       <c r="AT60" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AU60" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AV60" s="24" t="n"/>
@@ -18924,7 +19262,7 @@
       </c>
       <c r="BA60" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB60" s="24" t="inlineStr">
@@ -18934,12 +19272,12 @@
       </c>
       <c r="BC60" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD60" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE60" s="24" t="inlineStr">
@@ -18959,7 +19297,7 @@
       </c>
       <c r="BH60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI60" s="24" t="inlineStr">
@@ -18968,19 +19306,19 @@
         </is>
       </c>
       <c r="BJ60" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK60" s="26" t="n">
-        <v>-120</v>
+        <v>102</v>
       </c>
       <c r="BL60" s="27" t="n">
-        <v>1.833333</v>
+        <v>2.02</v>
       </c>
       <c r="BM60" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.49505</v>
       </c>
       <c r="BN60" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.492537</v>
       </c>
       <c r="BO60" s="28" t="n"/>
       <c r="BP60" s="25" t="n"/>
@@ -19021,22 +19359,22 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>57aef3476be84083</t>
+          <t>05a17390bf5f45aa</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:05Z</t>
+          <t>2026-08-10T23:45Z</t>
         </is>
       </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
-          <t>401816394</t>
+          <t>401816472</t>
         </is>
       </c>
       <c r="E61" s="24" t="inlineStr">
@@ -19046,26 +19384,26 @@
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="G61" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I61" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J61" s="25" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="K61" s="24" t="inlineStr">
         <is>
@@ -19073,32 +19411,32 @@
         </is>
       </c>
       <c r="L61" s="26" t="n">
-        <v>-115</v>
+        <v>-153</v>
       </c>
       <c r="M61" s="27" t="n">
-        <v>1.869565</v>
+        <v>1.653595</v>
       </c>
       <c r="N61" s="28" t="n">
-        <v>0.534884</v>
+        <v>0.604743</v>
       </c>
       <c r="O61" s="28" t="n">
-        <v>0.543008</v>
+        <v>0.660674</v>
       </c>
       <c r="P61" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q61" s="28" t="n">
-        <v>0.008123999999999999</v>
+        <v>0.055931</v>
       </c>
       <c r="R61" s="26" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="S61" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T61" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U61" s="24" t="inlineStr">
@@ -19117,7 +19455,7 @@
       <c r="AD61" s="24" t="n"/>
       <c r="AE61" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.98-4.16; raw selected-side p=0.6026, calibrated p=0.5430.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.48-5.28; raw selected-side p=0.7358, calibrated p=0.6607.</t>
         </is>
       </c>
       <c r="AF61" s="31" t="inlineStr">
@@ -19158,32 +19496,32 @@
       </c>
       <c r="AP61" s="24" t="inlineStr">
         <is>
-          <t>mlb-sf</t>
+          <t>mlb-phi</t>
         </is>
       </c>
       <c r="AQ61" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AR61" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AS61" s="24" t="inlineStr">
         <is>
-          <t>mlb-tex</t>
+          <t>mlb-stl</t>
         </is>
       </c>
       <c r="AT61" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AU61" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AV61" s="24" t="n"/>
@@ -19201,7 +19539,7 @@
       </c>
       <c r="BA61" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB61" s="24" t="inlineStr">
@@ -19211,12 +19549,12 @@
       </c>
       <c r="BC61" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD61" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE61" s="24" t="inlineStr">
@@ -19236,7 +19574,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -19245,19 +19583,19 @@
         </is>
       </c>
       <c r="BJ61" s="25" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK61" s="26" t="n">
-        <v>-115</v>
+        <v>-153</v>
       </c>
       <c r="BL61" s="27" t="n">
-        <v>1.869565</v>
+        <v>1.653595</v>
       </c>
       <c r="BM61" s="28" t="n">
-        <v>0.534884</v>
+        <v>0.604743</v>
       </c>
       <c r="BN61" s="28" t="n">
-        <v>0.532338</v>
+        <v>0.60199</v>
       </c>
       <c r="BO61" s="28" t="n"/>
       <c r="BP61" s="25" t="n"/>
@@ -19298,22 +19636,22 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>8bdbed487f214c46</t>
+          <t>28da1b67f4364356</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:10Z</t>
+          <t>2026-08-10T23:45Z</t>
         </is>
       </c>
       <c r="D62" s="24" t="inlineStr">
         <is>
-          <t>401816395</t>
+          <t>401816472</t>
         </is>
       </c>
       <c r="E62" s="24" t="inlineStr">
@@ -19323,26 +19661,26 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="G62" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I62" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J62" s="25" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="K62" s="24" t="inlineStr">
         <is>
@@ -19350,32 +19688,32 @@
         </is>
       </c>
       <c r="L62" s="26" t="n">
-        <v>-178</v>
+        <v>-125</v>
       </c>
       <c r="M62" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.8</v>
       </c>
       <c r="N62" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.555556</v>
       </c>
       <c r="O62" s="28" t="n">
-        <v>0.577535</v>
+        <v>0.513587</v>
       </c>
       <c r="P62" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q62" s="28" t="n">
-        <v>-0.062753</v>
+        <v>-0.041969</v>
       </c>
       <c r="R62" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S62" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T62" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U62" s="24" t="inlineStr">
@@ -19394,7 +19732,7 @@
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.31-4.86; raw selected-side p=0.6181, calibrated p=0.5775.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.48-5.28; raw selected-side p=0.5313, calibrated p=0.5136.</t>
         </is>
       </c>
       <c r="AF62" s="31" t="inlineStr">
@@ -19435,32 +19773,32 @@
       </c>
       <c r="AP62" s="24" t="inlineStr">
         <is>
-          <t>mlb-tor</t>
+          <t>mlb-phi</t>
         </is>
       </c>
       <c r="AQ62" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AR62" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AS62" s="24" t="inlineStr">
         <is>
-          <t>mlb-hou</t>
+          <t>mlb-stl</t>
         </is>
       </c>
       <c r="AT62" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AU62" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AV62" s="24" t="n"/>
@@ -19478,7 +19816,7 @@
       </c>
       <c r="BA62" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB62" s="24" t="inlineStr">
@@ -19488,12 +19826,12 @@
       </c>
       <c r="BC62" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD62" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE62" s="24" t="inlineStr">
@@ -19513,7 +19851,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -19522,19 +19860,19 @@
         </is>
       </c>
       <c r="BJ62" s="25" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="BK62" s="26" t="n">
-        <v>-178</v>
+        <v>-125</v>
       </c>
       <c r="BL62" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.8</v>
       </c>
       <c r="BM62" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.555556</v>
       </c>
       <c r="BN62" s="28" t="n">
-        <v>0.636816</v>
+        <v>0.552239</v>
       </c>
       <c r="BO62" s="28" t="n"/>
       <c r="BP62" s="25" t="n"/>
@@ -19575,22 +19913,22 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>d43d12ed43b34018</t>
+          <t>333fb38f8c60430b</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:10Z</t>
+          <t>2026-08-11T01:38Z</t>
         </is>
       </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
-          <t>401816395</t>
+          <t>401816478</t>
         </is>
       </c>
       <c r="E63" s="24" t="inlineStr">
@@ -19600,26 +19938,26 @@
       </c>
       <c r="F63" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="G63" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I63" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J63" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="K63" s="24" t="inlineStr">
         <is>
@@ -19627,32 +19965,32 @@
         </is>
       </c>
       <c r="L63" s="26" t="n">
-        <v>104</v>
+        <v>-156</v>
       </c>
       <c r="M63" s="27" t="n">
-        <v>2.04</v>
+        <v>1.641026</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.609375</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.516834</v>
+        <v>0.624526</v>
       </c>
       <c r="P63" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q63" s="28" t="n">
-        <v>0.026638</v>
+        <v>0.015151</v>
       </c>
       <c r="R63" s="26" t="n">
         <v>34</v>
       </c>
       <c r="S63" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T63" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U63" s="24" t="inlineStr">
@@ -19671,7 +20009,7 @@
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.31-4.86; raw selected-side p=0.5260, calibrated p=0.5168.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.49-4.65; raw selected-side p=0.6827, calibrated p=0.6245.</t>
         </is>
       </c>
       <c r="AF63" s="31" t="inlineStr">
@@ -19712,32 +20050,32 @@
       </c>
       <c r="AP63" s="24" t="inlineStr">
         <is>
-          <t>mlb-tor</t>
+          <t>mlb-tex</t>
         </is>
       </c>
       <c r="AQ63" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AR63" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AS63" s="24" t="inlineStr">
         <is>
-          <t>mlb-hou</t>
+          <t>mlb-laa</t>
         </is>
       </c>
       <c r="AT63" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AU63" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AV63" s="24" t="n"/>
@@ -19755,7 +20093,7 @@
       </c>
       <c r="BA63" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB63" s="24" t="inlineStr">
@@ -19765,12 +20103,12 @@
       </c>
       <c r="BC63" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD63" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE63" s="24" t="inlineStr">
@@ -19790,7 +20128,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -19799,19 +20137,19 @@
         </is>
       </c>
       <c r="BJ63" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK63" s="26" t="n">
-        <v>104</v>
+        <v>-156</v>
       </c>
       <c r="BL63" s="27" t="n">
-        <v>2.04</v>
+        <v>1.641026</v>
       </c>
       <c r="BM63" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.609375</v>
       </c>
       <c r="BN63" s="28" t="n">
-        <v>0.487562</v>
+        <v>0.606965</v>
       </c>
       <c r="BO63" s="28" t="n"/>
       <c r="BP63" s="25" t="n"/>
@@ -19852,22 +20190,22 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>9d6188233c84469f</t>
+          <t>8bc5d5c325484816</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:40Z</t>
+          <t>2026-08-11T01:38Z</t>
         </is>
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>401816396</t>
+          <t>401816478</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
@@ -19877,26 +20215,26 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="G64" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I64" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J64" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="K64" s="24" t="inlineStr">
         <is>
@@ -19904,32 +20242,32 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>-104</v>
+        <v>-115</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.869565</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.534884</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.6912700000000001</v>
+        <v>0.533074</v>
       </c>
       <c r="P64" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q64" s="28" t="n">
-        <v>0.181466</v>
+        <v>-0.00181</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="S64" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T64" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U64" s="24" t="inlineStr">
@@ -19948,7 +20286,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.49-6.29; raw selected-side p=0.7914, calibrated p=0.6913.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.49-4.65; raw selected-side p=0.6098, calibrated p=0.5331.</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -19989,32 +20327,32 @@
       </c>
       <c r="AP64" s="24" t="inlineStr">
         <is>
-          <t>mlb-tb</t>
+          <t>mlb-tex</t>
         </is>
       </c>
       <c r="AQ64" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AR64" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AS64" s="24" t="inlineStr">
         <is>
-          <t>mlb-col</t>
+          <t>mlb-laa</t>
         </is>
       </c>
       <c r="AT64" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AU64" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AV64" s="24" t="n"/>
@@ -20032,7 +20370,7 @@
       </c>
       <c r="BA64" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB64" s="24" t="inlineStr">
@@ -20042,12 +20380,12 @@
       </c>
       <c r="BC64" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD64" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE64" s="24" t="inlineStr">
@@ -20067,7 +20405,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -20076,19 +20414,19 @@
         </is>
       </c>
       <c r="BJ64" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK64" s="26" t="n">
-        <v>-104</v>
+        <v>-115</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.869565</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.534884</v>
       </c>
       <c r="BN64" s="28" t="n">
-        <v>0.507463</v>
+        <v>0.532338</v>
       </c>
       <c r="BO64" s="28" t="n"/>
       <c r="BP64" s="25" t="n"/>
@@ -20122,29 +20460,29 @@
       <c r="CR64" s="24" t="n"/>
       <c r="CS64" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>b2a3b70378ef493f</t>
+          <t>68a261682a5d40c4</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:40Z</t>
+          <t>2026-08-11T01:40Z</t>
         </is>
       </c>
       <c r="D65" s="24" t="inlineStr">
         <is>
-          <t>401816396</t>
+          <t>401816473</t>
         </is>
       </c>
       <c r="E65" s="24" t="inlineStr">
@@ -20154,26 +20492,26 @@
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="G65" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I65" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J65" s="25" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="K65" s="24" t="inlineStr">
         <is>
@@ -20181,32 +20519,32 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-117</v>
+        <v>-111</v>
       </c>
       <c r="M65" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.900901</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.526066</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.544905</v>
+        <v>0.578395</v>
       </c>
       <c r="P65" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q65" s="28" t="n">
-        <v>0.005734</v>
+        <v>0.052329</v>
       </c>
       <c r="R65" s="26" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="S65" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T65" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U65" s="24" t="inlineStr">
@@ -20225,7 +20563,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.49-6.29; raw selected-side p=0.6081, calibrated p=0.5449.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.36-4.90; raw selected-side p=0.6150, calibrated p=0.5784.</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -20266,32 +20604,32 @@
       </c>
       <c r="AP65" s="24" t="inlineStr">
         <is>
-          <t>mlb-tb</t>
+          <t>mlb-col</t>
         </is>
       </c>
       <c r="AQ65" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AR65" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AS65" s="24" t="inlineStr">
         <is>
-          <t>mlb-col</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT65" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU65" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV65" s="24" t="n"/>
@@ -20309,7 +20647,7 @@
       </c>
       <c r="BA65" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB65" s="24" t="inlineStr">
@@ -20319,12 +20657,12 @@
       </c>
       <c r="BC65" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD65" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE65" s="24" t="inlineStr">
@@ -20344,7 +20682,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -20353,19 +20691,19 @@
         </is>
       </c>
       <c r="BJ65" s="25" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK65" s="26" t="n">
-        <v>-117</v>
+        <v>-111</v>
       </c>
       <c r="BL65" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.900901</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.526066</v>
       </c>
       <c r="BN65" s="28" t="n">
-        <v>0.537313</v>
+        <v>0.522388</v>
       </c>
       <c r="BO65" s="28" t="n"/>
       <c r="BP65" s="25" t="n"/>
@@ -20406,22 +20744,22 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>87a3403819ca4958</t>
+          <t>3993bbda7f5843c3</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T01:40Z</t>
+          <t>2026-08-11T01:40Z</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
-          <t>401816398</t>
+          <t>401816473</t>
         </is>
       </c>
       <c r="E66" s="24" t="inlineStr">
@@ -20431,7 +20769,7 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="G66" s="24" t="inlineStr">
@@ -20441,16 +20779,16 @@
       </c>
       <c r="H66" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I66" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J66" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="K66" s="24" t="inlineStr">
         <is>
@@ -20458,32 +20796,32 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>-178</v>
+        <v>-113</v>
       </c>
       <c r="M66" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.884956</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.530516</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.543418</v>
+        <v>0.514618</v>
       </c>
       <c r="P66" s="28" t="n">
-        <v>0.042131</v>
+        <v>0.05172</v>
       </c>
       <c r="Q66" s="28" t="n">
-        <v>-0.09687</v>
+        <v>-0.015898</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S66" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T66" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U66" s="24" t="inlineStr">
@@ -20502,7 +20840,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.09-5.16; raw selected-side p=0.5661, calibrated p=0.5434.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.36-4.90; raw selected-side p=0.5355, calibrated p=0.5146.</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -20543,17 +20881,17 @@
       </c>
       <c r="AP66" s="24" t="inlineStr">
         <is>
-          <t>mlb-sd</t>
+          <t>mlb-col</t>
         </is>
       </c>
       <c r="AQ66" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AR66" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AS66" s="24" t="inlineStr">
@@ -20586,7 +20924,7 @@
       </c>
       <c r="BA66" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB66" s="24" t="inlineStr">
@@ -20596,12 +20934,12 @@
       </c>
       <c r="BC66" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD66" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE66" s="24" t="inlineStr">
@@ -20621,7 +20959,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -20630,19 +20968,19 @@
         </is>
       </c>
       <c r="BJ66" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK66" s="26" t="n">
-        <v>-178</v>
+        <v>-113</v>
       </c>
       <c r="BL66" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.884956</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.530516</v>
       </c>
       <c r="BN66" s="28" t="n">
-        <v>0.636816</v>
+        <v>0.527363</v>
       </c>
       <c r="BO66" s="28" t="n"/>
       <c r="BP66" s="25" t="n"/>
@@ -20683,22 +21021,22 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>df3742dc80134149</t>
+          <t>2063c081a59d43be</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T01:40Z</t>
+          <t>2026-08-11T01:40Z</t>
         </is>
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>401816398</t>
+          <t>401816476</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
@@ -20708,26 +21046,26 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="G67" s="24" t="inlineStr">
+        <is>
           <t>San Diego Padres</t>
         </is>
       </c>
-      <c r="G67" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
       <c r="H67" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I67" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J67" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="K67" s="24" t="inlineStr">
         <is>
@@ -20735,32 +21073,32 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>-125</v>
+        <v>-163</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>1.8</v>
+        <v>1.613497</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.619772</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.520781</v>
+        <v>0.591614</v>
       </c>
       <c r="P67" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q67" s="28" t="n">
-        <v>-0.034775</v>
+        <v>-0.028158</v>
       </c>
       <c r="R67" s="26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S67" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T67" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U67" s="24" t="inlineStr">
@@ -20779,7 +21117,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.09-5.16; raw selected-side p=0.5375, calibrated p=0.5208.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.48-4.13; raw selected-side p=0.6344, calibrated p=0.5916.</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -20820,32 +21158,32 @@
       </c>
       <c r="AP67" s="24" t="inlineStr">
         <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AQ67" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AR67" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AS67" s="24" t="inlineStr">
+        <is>
           <t>mlb-sd</t>
         </is>
       </c>
-      <c r="AQ67" s="24" t="inlineStr">
+      <c r="AT67" s="24" t="inlineStr">
         <is>
           <t>San Diego Padres</t>
         </is>
       </c>
-      <c r="AR67" s="24" t="inlineStr">
+      <c r="AU67" s="24" t="inlineStr">
         <is>
           <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="AS67" s="24" t="inlineStr">
-        <is>
-          <t>mlb-ari</t>
-        </is>
-      </c>
-      <c r="AT67" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="AU67" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV67" s="24" t="n"/>
@@ -20863,7 +21201,7 @@
       </c>
       <c r="BA67" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB67" s="24" t="inlineStr">
@@ -20873,12 +21211,12 @@
       </c>
       <c r="BC67" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD67" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE67" s="24" t="inlineStr">
@@ -20898,7 +21236,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-10T16:35:10.426686Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -20907,19 +21245,19 @@
         </is>
       </c>
       <c r="BJ67" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK67" s="26" t="n">
-        <v>-125</v>
+        <v>-163</v>
       </c>
       <c r="BL67" s="27" t="n">
-        <v>1.8</v>
+        <v>1.613497</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.619772</v>
       </c>
       <c r="BN67" s="28" t="n">
-        <v>0.552239</v>
+        <v>0.616915</v>
       </c>
       <c r="BO67" s="28" t="n"/>
       <c r="BP67" s="25" t="n"/>
@@ -20957,6 +21295,1945 @@
         </is>
       </c>
     </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>e8120b117d2c438c</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T01:40Z</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>401816476</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="G68" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="H68" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I68" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J68" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K68" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L68" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M68" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N68" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O68" s="28" t="n">
+        <v>0.520903</v>
+      </c>
+      <c r="P68" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q68" s="28" t="n">
+        <v>0.070453</v>
+      </c>
+      <c r="R68" s="26" t="n">
+        <v>61</v>
+      </c>
+      <c r="S68" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U68" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V68" s="24" t="n"/>
+      <c r="W68" s="26" t="n"/>
+      <c r="X68" s="26" t="n"/>
+      <c r="Y68" s="25" t="n"/>
+      <c r="Z68" s="26" t="n"/>
+      <c r="AA68" s="28" t="n"/>
+      <c r="AB68" s="28" t="n"/>
+      <c r="AC68" s="30" t="n"/>
+      <c r="AD68" s="24" t="n"/>
+      <c r="AE68" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.48-4.13; raw selected-side p=0.5608, calibrated p=0.5209.</t>
+        </is>
+      </c>
+      <c r="AF68" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG68" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH68" s="24" t="n"/>
+      <c r="AI68" s="31" t="n"/>
+      <c r="AJ68" s="31" t="n"/>
+      <c r="AK68" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL68" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM68" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN68" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO68" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP68" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AQ68" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AR68" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AS68" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sd</t>
+        </is>
+      </c>
+      <c r="AT68" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AU68" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AV68" s="24" t="n"/>
+      <c r="AW68" s="24" t="n"/>
+      <c r="AX68" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY68" s="24" t="n"/>
+      <c r="AZ68" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA68" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BB68" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC68" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="BD68" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BE68" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF68" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG68" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="BI68" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ68" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BK68" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL68" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM68" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN68" s="28" t="n">
+        <v>0.447761</v>
+      </c>
+      <c r="BO68" s="28" t="n"/>
+      <c r="BP68" s="25" t="n"/>
+      <c r="BQ68" s="27" t="n"/>
+      <c r="BR68" s="28" t="n"/>
+      <c r="BS68" s="28" t="n"/>
+      <c r="BT68" s="28" t="n"/>
+      <c r="BU68" s="25" t="n"/>
+      <c r="BV68" s="29" t="n"/>
+      <c r="BW68" s="24" t="n"/>
+      <c r="BX68" s="30" t="n"/>
+      <c r="BY68" s="27" t="n"/>
+      <c r="BZ68" s="24" t="n"/>
+      <c r="CA68" s="31" t="n"/>
+      <c r="CB68" s="24" t="n"/>
+      <c r="CC68" s="24" t="n"/>
+      <c r="CD68" s="24" t="n"/>
+      <c r="CE68" s="24" t="n"/>
+      <c r="CF68" s="24" t="n"/>
+      <c r="CG68" s="24" t="n"/>
+      <c r="CH68" s="24" t="n"/>
+      <c r="CI68" s="24" t="n"/>
+      <c r="CJ68" s="24" t="n"/>
+      <c r="CK68" s="24" t="n"/>
+      <c r="CL68" s="24" t="n"/>
+      <c r="CM68" s="24" t="n"/>
+      <c r="CN68" s="24" t="n"/>
+      <c r="CO68" s="24" t="n"/>
+      <c r="CP68" s="24" t="n"/>
+      <c r="CQ68" s="24" t="n"/>
+      <c r="CR68" s="24" t="n"/>
+      <c r="CS68" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>41fda822265d4e50</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T01:40Z</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>401816477</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="G69" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="H69" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I69" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J69" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K69" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L69" s="26" t="n">
+        <v>-106</v>
+      </c>
+      <c r="M69" s="27" t="n">
+        <v>1.943396</v>
+      </c>
+      <c r="N69" s="28" t="n">
+        <v>0.514563</v>
+      </c>
+      <c r="O69" s="28" t="n">
+        <v>0.645922</v>
+      </c>
+      <c r="P69" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q69" s="28" t="n">
+        <v>0.131359</v>
+      </c>
+      <c r="R69" s="26" t="n">
+        <v>91</v>
+      </c>
+      <c r="S69" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T69" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U69" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V69" s="24" t="n"/>
+      <c r="W69" s="26" t="n"/>
+      <c r="X69" s="26" t="n"/>
+      <c r="Y69" s="25" t="n"/>
+      <c r="Z69" s="26" t="n"/>
+      <c r="AA69" s="28" t="n"/>
+      <c r="AB69" s="28" t="n"/>
+      <c r="AC69" s="30" t="n"/>
+      <c r="AD69" s="24" t="n"/>
+      <c r="AE69" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.71-5.38; raw selected-side p=0.7141, calibrated p=0.6459.</t>
+        </is>
+      </c>
+      <c r="AF69" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG69" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH69" s="24" t="n"/>
+      <c r="AI69" s="31" t="n"/>
+      <c r="AJ69" s="31" t="n"/>
+      <c r="AK69" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL69" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM69" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN69" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO69" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP69" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tb</t>
+        </is>
+      </c>
+      <c r="AQ69" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AR69" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AS69" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ath</t>
+        </is>
+      </c>
+      <c r="AT69" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AU69" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AV69" s="24" t="n"/>
+      <c r="AW69" s="24" t="n"/>
+      <c r="AX69" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY69" s="24" t="n"/>
+      <c r="AZ69" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA69" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BB69" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC69" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="BD69" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BE69" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF69" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG69" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH69" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="BI69" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ69" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK69" s="26" t="n">
+        <v>-106</v>
+      </c>
+      <c r="BL69" s="27" t="n">
+        <v>1.943396</v>
+      </c>
+      <c r="BM69" s="28" t="n">
+        <v>0.514563</v>
+      </c>
+      <c r="BN69" s="28" t="n">
+        <v>0.5124379999999999</v>
+      </c>
+      <c r="BO69" s="28" t="n"/>
+      <c r="BP69" s="25" t="n"/>
+      <c r="BQ69" s="27" t="n"/>
+      <c r="BR69" s="28" t="n"/>
+      <c r="BS69" s="28" t="n"/>
+      <c r="BT69" s="28" t="n"/>
+      <c r="BU69" s="25" t="n"/>
+      <c r="BV69" s="29" t="n"/>
+      <c r="BW69" s="24" t="n"/>
+      <c r="BX69" s="30" t="n"/>
+      <c r="BY69" s="27" t="n"/>
+      <c r="BZ69" s="24" t="n"/>
+      <c r="CA69" s="31" t="n"/>
+      <c r="CB69" s="24" t="n"/>
+      <c r="CC69" s="24" t="n"/>
+      <c r="CD69" s="24" t="n"/>
+      <c r="CE69" s="24" t="n"/>
+      <c r="CF69" s="24" t="n"/>
+      <c r="CG69" s="24" t="n"/>
+      <c r="CH69" s="24" t="n"/>
+      <c r="CI69" s="24" t="n"/>
+      <c r="CJ69" s="24" t="n"/>
+      <c r="CK69" s="24" t="n"/>
+      <c r="CL69" s="24" t="n"/>
+      <c r="CM69" s="24" t="n"/>
+      <c r="CN69" s="24" t="n"/>
+      <c r="CO69" s="24" t="n"/>
+      <c r="CP69" s="24" t="n"/>
+      <c r="CQ69" s="24" t="n"/>
+      <c r="CR69" s="24" t="n"/>
+      <c r="CS69" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="36" customHeight="1">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>67eb2e89c4774b3d</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T01:40Z</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr">
+        <is>
+          <t>401816477</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F70" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="G70" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="H70" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I70" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J70" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K70" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L70" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M70" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N70" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O70" s="28" t="n">
+        <v>0.505862</v>
+      </c>
+      <c r="P70" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q70" s="28" t="n">
+        <v>-0.024654</v>
+      </c>
+      <c r="R70" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="S70" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U70" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V70" s="24" t="n"/>
+      <c r="W70" s="26" t="n"/>
+      <c r="X70" s="26" t="n"/>
+      <c r="Y70" s="25" t="n"/>
+      <c r="Z70" s="26" t="n"/>
+      <c r="AA70" s="28" t="n"/>
+      <c r="AB70" s="28" t="n"/>
+      <c r="AC70" s="30" t="n"/>
+      <c r="AD70" s="24" t="n"/>
+      <c r="AE70" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.71-5.38; raw selected-side p=0.5002, calibrated p=0.5059.</t>
+        </is>
+      </c>
+      <c r="AF70" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG70" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH70" s="24" t="n"/>
+      <c r="AI70" s="31" t="n"/>
+      <c r="AJ70" s="31" t="n"/>
+      <c r="AK70" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL70" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM70" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN70" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO70" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP70" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tb</t>
+        </is>
+      </c>
+      <c r="AQ70" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AR70" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AS70" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ath</t>
+        </is>
+      </c>
+      <c r="AT70" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AU70" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AV70" s="24" t="n"/>
+      <c r="AW70" s="24" t="n"/>
+      <c r="AX70" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY70" s="24" t="n"/>
+      <c r="AZ70" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA70" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BB70" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC70" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="BD70" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BE70" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF70" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG70" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH70" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="BI70" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ70" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BK70" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL70" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM70" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN70" s="28" t="n">
+        <v>0.524752</v>
+      </c>
+      <c r="BO70" s="28" t="n"/>
+      <c r="BP70" s="25" t="n"/>
+      <c r="BQ70" s="27" t="n"/>
+      <c r="BR70" s="28" t="n"/>
+      <c r="BS70" s="28" t="n"/>
+      <c r="BT70" s="28" t="n"/>
+      <c r="BU70" s="25" t="n"/>
+      <c r="BV70" s="29" t="n"/>
+      <c r="BW70" s="24" t="n"/>
+      <c r="BX70" s="30" t="n"/>
+      <c r="BY70" s="27" t="n"/>
+      <c r="BZ70" s="24" t="n"/>
+      <c r="CA70" s="31" t="n"/>
+      <c r="CB70" s="24" t="n"/>
+      <c r="CC70" s="24" t="n"/>
+      <c r="CD70" s="24" t="n"/>
+      <c r="CE70" s="24" t="n"/>
+      <c r="CF70" s="24" t="n"/>
+      <c r="CG70" s="24" t="n"/>
+      <c r="CH70" s="24" t="n"/>
+      <c r="CI70" s="24" t="n"/>
+      <c r="CJ70" s="24" t="n"/>
+      <c r="CK70" s="24" t="n"/>
+      <c r="CL70" s="24" t="n"/>
+      <c r="CM70" s="24" t="n"/>
+      <c r="CN70" s="24" t="n"/>
+      <c r="CO70" s="24" t="n"/>
+      <c r="CP70" s="24" t="n"/>
+      <c r="CQ70" s="24" t="n"/>
+      <c r="CR70" s="24" t="n"/>
+      <c r="CS70" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>830c9632059c42c9</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T01:45Z</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>401816474</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="H71" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I71" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J71" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K71" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L71" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M71" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N71" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O71" s="28" t="n">
+        <v>0.621289</v>
+      </c>
+      <c r="P71" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q71" s="28" t="n">
+        <v>0.061818</v>
+      </c>
+      <c r="R71" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="S71" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T71" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U71" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V71" s="24" t="n"/>
+      <c r="W71" s="26" t="n"/>
+      <c r="X71" s="26" t="n"/>
+      <c r="Y71" s="25" t="n"/>
+      <c r="Z71" s="26" t="n"/>
+      <c r="AA71" s="28" t="n"/>
+      <c r="AB71" s="28" t="n"/>
+      <c r="AC71" s="30" t="n"/>
+      <c r="AD71" s="24" t="n"/>
+      <c r="AE71" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.41-4.47; raw selected-side p=0.6780, calibrated p=0.6213.</t>
+        </is>
+      </c>
+      <c r="AF71" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG71" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH71" s="24" t="n"/>
+      <c r="AI71" s="31" t="n"/>
+      <c r="AJ71" s="31" t="n"/>
+      <c r="AK71" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL71" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM71" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN71" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO71" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP71" s="24" t="inlineStr">
+        <is>
+          <t>mlb-hou</t>
+        </is>
+      </c>
+      <c r="AQ71" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="AR71" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="AS71" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sf</t>
+        </is>
+      </c>
+      <c r="AT71" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AU71" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AV71" s="24" t="n"/>
+      <c r="AW71" s="24" t="n"/>
+      <c r="AX71" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY71" s="24" t="n"/>
+      <c r="AZ71" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA71" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BB71" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC71" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="BD71" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BE71" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF71" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG71" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH71" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="BI71" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ71" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK71" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL71" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM71" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN71" s="28" t="n">
+        <v>0.557214</v>
+      </c>
+      <c r="BO71" s="28" t="n"/>
+      <c r="BP71" s="25" t="n"/>
+      <c r="BQ71" s="27" t="n"/>
+      <c r="BR71" s="28" t="n"/>
+      <c r="BS71" s="28" t="n"/>
+      <c r="BT71" s="28" t="n"/>
+      <c r="BU71" s="25" t="n"/>
+      <c r="BV71" s="29" t="n"/>
+      <c r="BW71" s="24" t="n"/>
+      <c r="BX71" s="30" t="n"/>
+      <c r="BY71" s="27" t="n"/>
+      <c r="BZ71" s="24" t="n"/>
+      <c r="CA71" s="31" t="n"/>
+      <c r="CB71" s="24" t="n"/>
+      <c r="CC71" s="24" t="n"/>
+      <c r="CD71" s="24" t="n"/>
+      <c r="CE71" s="24" t="n"/>
+      <c r="CF71" s="24" t="n"/>
+      <c r="CG71" s="24" t="n"/>
+      <c r="CH71" s="24" t="n"/>
+      <c r="CI71" s="24" t="n"/>
+      <c r="CJ71" s="24" t="n"/>
+      <c r="CK71" s="24" t="n"/>
+      <c r="CL71" s="24" t="n"/>
+      <c r="CM71" s="24" t="n"/>
+      <c r="CN71" s="24" t="n"/>
+      <c r="CO71" s="24" t="n"/>
+      <c r="CP71" s="24" t="n"/>
+      <c r="CQ71" s="24" t="n"/>
+      <c r="CR71" s="24" t="n"/>
+      <c r="CS71" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="36" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>f04ad344d9194687</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T01:45Z</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr">
+        <is>
+          <t>401816474</t>
+        </is>
+      </c>
+      <c r="E72" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F72" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="G72" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="H72" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I72" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J72" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K72" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L72" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M72" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N72" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O72" s="28" t="n">
+        <v>0.507502</v>
+      </c>
+      <c r="P72" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q72" s="28" t="n">
+        <v>0.026733</v>
+      </c>
+      <c r="R72" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="S72" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U72" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V72" s="24" t="n"/>
+      <c r="W72" s="26" t="n"/>
+      <c r="X72" s="26" t="n"/>
+      <c r="Y72" s="25" t="n"/>
+      <c r="Z72" s="26" t="n"/>
+      <c r="AA72" s="28" t="n"/>
+      <c r="AB72" s="28" t="n"/>
+      <c r="AC72" s="30" t="n"/>
+      <c r="AD72" s="24" t="n"/>
+      <c r="AE72" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.41-4.47; raw selected-side p=0.5069, calibrated p=0.5075.</t>
+        </is>
+      </c>
+      <c r="AF72" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG72" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH72" s="24" t="n"/>
+      <c r="AI72" s="31" t="n"/>
+      <c r="AJ72" s="31" t="n"/>
+      <c r="AK72" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL72" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM72" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN72" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO72" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP72" s="24" t="inlineStr">
+        <is>
+          <t>mlb-hou</t>
+        </is>
+      </c>
+      <c r="AQ72" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="AR72" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="AS72" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sf</t>
+        </is>
+      </c>
+      <c r="AT72" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AU72" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AV72" s="24" t="n"/>
+      <c r="AW72" s="24" t="n"/>
+      <c r="AX72" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY72" s="24" t="n"/>
+      <c r="AZ72" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA72" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BB72" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC72" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="BD72" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BE72" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF72" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG72" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH72" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="BI72" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ72" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BK72" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL72" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM72" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN72" s="28" t="n">
+        <v>0.477612</v>
+      </c>
+      <c r="BO72" s="28" t="n"/>
+      <c r="BP72" s="25" t="n"/>
+      <c r="BQ72" s="27" t="n"/>
+      <c r="BR72" s="28" t="n"/>
+      <c r="BS72" s="28" t="n"/>
+      <c r="BT72" s="28" t="n"/>
+      <c r="BU72" s="25" t="n"/>
+      <c r="BV72" s="29" t="n"/>
+      <c r="BW72" s="24" t="n"/>
+      <c r="BX72" s="30" t="n"/>
+      <c r="BY72" s="27" t="n"/>
+      <c r="BZ72" s="24" t="n"/>
+      <c r="CA72" s="31" t="n"/>
+      <c r="CB72" s="24" t="n"/>
+      <c r="CC72" s="24" t="n"/>
+      <c r="CD72" s="24" t="n"/>
+      <c r="CE72" s="24" t="n"/>
+      <c r="CF72" s="24" t="n"/>
+      <c r="CG72" s="24" t="n"/>
+      <c r="CH72" s="24" t="n"/>
+      <c r="CI72" s="24" t="n"/>
+      <c r="CJ72" s="24" t="n"/>
+      <c r="CK72" s="24" t="n"/>
+      <c r="CL72" s="24" t="n"/>
+      <c r="CM72" s="24" t="n"/>
+      <c r="CN72" s="24" t="n"/>
+      <c r="CO72" s="24" t="n"/>
+      <c r="CP72" s="24" t="n"/>
+      <c r="CQ72" s="24" t="n"/>
+      <c r="CR72" s="24" t="n"/>
+      <c r="CS72" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="36" customHeight="1">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>655b4376df724abd</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T02:10Z</t>
+        </is>
+      </c>
+      <c r="D73" s="24" t="inlineStr">
+        <is>
+          <t>401816475</t>
+        </is>
+      </c>
+      <c r="E73" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F73" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="G73" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="H73" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I73" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J73" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K73" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L73" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M73" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N73" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O73" s="28" t="n">
+        <v>0.570286</v>
+      </c>
+      <c r="P73" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q73" s="28" t="n">
+        <v>0.100802</v>
+      </c>
+      <c r="R73" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="S73" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T73" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U73" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V73" s="24" t="n"/>
+      <c r="W73" s="26" t="n"/>
+      <c r="X73" s="26" t="n"/>
+      <c r="Y73" s="25" t="n"/>
+      <c r="Z73" s="26" t="n"/>
+      <c r="AA73" s="28" t="n"/>
+      <c r="AB73" s="28" t="n"/>
+      <c r="AC73" s="30" t="n"/>
+      <c r="AD73" s="24" t="n"/>
+      <c r="AE73" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.01-4.71; raw selected-side p=0.6031, calibrated p=0.5703.</t>
+        </is>
+      </c>
+      <c r="AF73" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG73" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH73" s="24" t="n"/>
+      <c r="AI73" s="31" t="n"/>
+      <c r="AJ73" s="31" t="n"/>
+      <c r="AK73" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL73" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM73" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN73" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO73" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP73" s="24" t="inlineStr">
+        <is>
+          <t>mlb-kc</t>
+        </is>
+      </c>
+      <c r="AQ73" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AR73" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AS73" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AT73" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AU73" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AV73" s="24" t="n"/>
+      <c r="AW73" s="24" t="n"/>
+      <c r="AX73" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY73" s="24" t="n"/>
+      <c r="AZ73" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA73" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BB73" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC73" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="BD73" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BE73" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF73" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG73" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH73" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="BI73" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ73" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK73" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL73" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM73" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN73" s="28" t="n">
+        <v>0.467662</v>
+      </c>
+      <c r="BO73" s="28" t="n"/>
+      <c r="BP73" s="25" t="n"/>
+      <c r="BQ73" s="27" t="n"/>
+      <c r="BR73" s="28" t="n"/>
+      <c r="BS73" s="28" t="n"/>
+      <c r="BT73" s="28" t="n"/>
+      <c r="BU73" s="25" t="n"/>
+      <c r="BV73" s="29" t="n"/>
+      <c r="BW73" s="24" t="n"/>
+      <c r="BX73" s="30" t="n"/>
+      <c r="BY73" s="27" t="n"/>
+      <c r="BZ73" s="24" t="n"/>
+      <c r="CA73" s="31" t="n"/>
+      <c r="CB73" s="24" t="n"/>
+      <c r="CC73" s="24" t="n"/>
+      <c r="CD73" s="24" t="n"/>
+      <c r="CE73" s="24" t="n"/>
+      <c r="CF73" s="24" t="n"/>
+      <c r="CG73" s="24" t="n"/>
+      <c r="CH73" s="24" t="n"/>
+      <c r="CI73" s="24" t="n"/>
+      <c r="CJ73" s="24" t="n"/>
+      <c r="CK73" s="24" t="n"/>
+      <c r="CL73" s="24" t="n"/>
+      <c r="CM73" s="24" t="n"/>
+      <c r="CN73" s="24" t="n"/>
+      <c r="CO73" s="24" t="n"/>
+      <c r="CP73" s="24" t="n"/>
+      <c r="CQ73" s="24" t="n"/>
+      <c r="CR73" s="24" t="n"/>
+      <c r="CS73" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="36" customHeight="1">
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>d6a49e6055564cc1</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T02:10Z</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>401816475</t>
+        </is>
+      </c>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F74" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="G74" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="H74" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I74" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J74" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K74" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L74" s="26" t="n">
+        <v>115</v>
+      </c>
+      <c r="M74" s="27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N74" s="28" t="n">
+        <v>0.465116</v>
+      </c>
+      <c r="O74" s="28" t="n">
+        <v>0.522468</v>
+      </c>
+      <c r="P74" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q74" s="28" t="n">
+        <v>0.057352</v>
+      </c>
+      <c r="R74" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="S74" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U74" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V74" s="24" t="n"/>
+      <c r="W74" s="26" t="n"/>
+      <c r="X74" s="26" t="n"/>
+      <c r="Y74" s="25" t="n"/>
+      <c r="Z74" s="26" t="n"/>
+      <c r="AA74" s="28" t="n"/>
+      <c r="AB74" s="28" t="n"/>
+      <c r="AC74" s="30" t="n"/>
+      <c r="AD74" s="24" t="n"/>
+      <c r="AE74" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.01-4.71; raw selected-side p=0.5671, calibrated p=0.5225.</t>
+        </is>
+      </c>
+      <c r="AF74" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG74" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH74" s="24" t="n"/>
+      <c r="AI74" s="31" t="n"/>
+      <c r="AJ74" s="31" t="n"/>
+      <c r="AK74" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL74" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM74" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN74" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO74" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP74" s="24" t="inlineStr">
+        <is>
+          <t>mlb-kc</t>
+        </is>
+      </c>
+      <c r="AQ74" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AR74" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AS74" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AT74" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AU74" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AV74" s="24" t="n"/>
+      <c r="AW74" s="24" t="n"/>
+      <c r="AX74" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY74" s="24" t="n"/>
+      <c r="AZ74" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA74" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BB74" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC74" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="BD74" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BE74" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF74" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG74" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH74" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:10.426686Z</t>
+        </is>
+      </c>
+      <c r="BI74" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ74" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BK74" s="26" t="n">
+        <v>115</v>
+      </c>
+      <c r="BL74" s="27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM74" s="28" t="n">
+        <v>0.465116</v>
+      </c>
+      <c r="BN74" s="28" t="n">
+        <v>0.462687</v>
+      </c>
+      <c r="BO74" s="28" t="n"/>
+      <c r="BP74" s="25" t="n"/>
+      <c r="BQ74" s="27" t="n"/>
+      <c r="BR74" s="28" t="n"/>
+      <c r="BS74" s="28" t="n"/>
+      <c r="BT74" s="28" t="n"/>
+      <c r="BU74" s="25" t="n"/>
+      <c r="BV74" s="29" t="n"/>
+      <c r="BW74" s="24" t="n"/>
+      <c r="BX74" s="30" t="n"/>
+      <c r="BY74" s="27" t="n"/>
+      <c r="BZ74" s="24" t="n"/>
+      <c r="CA74" s="31" t="n"/>
+      <c r="CB74" s="24" t="n"/>
+      <c r="CC74" s="24" t="n"/>
+      <c r="CD74" s="24" t="n"/>
+      <c r="CE74" s="24" t="n"/>
+      <c r="CF74" s="24" t="n"/>
+      <c r="CG74" s="24" t="n"/>
+      <c r="CH74" s="24" t="n"/>
+      <c r="CI74" s="24" t="n"/>
+      <c r="CJ74" s="24" t="n"/>
+      <c r="CK74" s="24" t="n"/>
+      <c r="CL74" s="24" t="n"/>
+      <c r="CM74" s="24" t="n"/>
+      <c r="CN74" s="24" t="n"/>
+      <c r="CO74" s="24" t="n"/>
+      <c r="CP74" s="24" t="n"/>
+      <c r="CQ74" s="24" t="n"/>
+      <c r="CR74" s="24" t="n"/>
+      <c r="CS74" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
